--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -8,7 +8,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="elevator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tag-day" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endos-junction" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="facility" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -3931,7 +3930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4913,267 +4912,244 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>facility.exit_narration</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>junction.exit_narration</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>The facility door seals behind you. The corridor stretches ahead.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Leaving the facility</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>facility.endo_appears</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>junction.endo_appears</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Endo joins — no words</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>facility.endo.shelters</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>junction.endo.shelters</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>He points ahead. Then at a marker on the wall — a shelter symbol.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Endo gestures toward shelter — marker appears</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>facility.endo.iron_warn</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>junction.endo.iron_warn</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>He stops. Holds out an arm. Shakes his head slowly.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Endo blocks the iron path — marker on safe route</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>facility.endo.dusk</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>junction.endo.dusk</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>He taps the wall. Points at the dimming light. Walks faster.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Endo notices dusk — urgency without words</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>facility.endo.shelter</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>junction.endo.shelter</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>He stops at a door. Opens it. Steps aside.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Endo at the shelter entrance</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>facility.night_narration</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>junction.night_narration</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>First night</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>facility.endo.rest</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>junction.endo.rest</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>He settles against the wall. Watches the door.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Endo takes watch — same posture as junction</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>facility.dawn</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>junction.dawn</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Day 2. Dawn.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Morning — waits for click</t>
         </is>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -3039,6 +3039,11 @@
           <t>tag_day.nk_chat.01</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3089,6 +3094,11 @@
           <t>tag_day.nk_chat.02</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3160,6 +3170,11 @@
           <t>tag_day.nk_chat.03</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3210,6 +3225,11 @@
           <t>tag_day.nk_chat.04</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3260,6 +3280,11 @@
           <t>tag_day.nk_chat.05</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3331,6 +3356,11 @@
           <t>tag_day.nk_chat.06</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3386,6 +3416,11 @@
           <t>tag_day.nk_chat.07</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3436,6 +3471,11 @@
           <t>tag_day.nk_chat.08</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3486,6 +3526,11 @@
           <t>tag_day.nk_chat.09</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>normal</t>
@@ -3533,6 +3578,11 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NK-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -8,6 +8,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="elevator" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tag-day" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endos-junction" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channels" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="residential-rings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockout" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -5208,4 +5212,1996 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>channels.narration.enter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>The corridor opens. Water runs along the floor in shallow channels. The air is different here — cleaner where the water flows, stale where it pools.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>First view of the Perivascular Channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>channels.aster.fluid</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fluid dynamics are still active in this section. Flow rate correlates with atmospheric quality. Where it moves, the readings are clean.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aster reads the data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>channels.peris.sound</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Listen. You can hear it. The moving water sounds different from the still water.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Peris reads by ear</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>channels.endo.stop</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>He stops at the edge of a stagnant pool. Shakes his head. Points to the flowing channel beside it.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Endo: stagnant = danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>channels.aster.stagnant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Iron concentration spikes near the stagnant sections. The standing water is concentrating the deposits.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aster confirms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>channels.peris.thick</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The air is heavier here. Like breathing through cloth.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Peris feels biofilm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>channels.narration.flora</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Something is growing where the water seeps into the wall. Faint. Not quite alive, not quite dead.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>First wild flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>channels.peris.touch</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>It responds to me. I just... touched it, and it brightened.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Peris discovers tending</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>channels.aster.glow</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bioluminescence increased by 40% on contact. Whatever you did, the growth is producing more light now.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aster measures it</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>channels.peris.always</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>I didn't do anything. Plants just... respond to me. They always have.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>She doesn't know why</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>channels.narration.branch</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The channels branch. One path flows steadily forward. Another leads into silence.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Route choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>channels.endo.point</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>He points toward the flowing channel. Then at the silent branch, and draws a finger across his throat.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>That way is death</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>channels.narration.body</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A figure in the drainage channel. Still. The water flows around them. They stopped moving a long time ago.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>First lootable corpse</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>channels.endo.kneel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>He kneels beside the body. A brief pause. Then his hands move — practiced, efficient. He stands with something in his palm.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Endo demonstrates nutrient absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>channels.peris.what</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>What did he just...?</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Peris processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>channels.aster.nutrients</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Organic nutrient absorption. The biological matter still has caloric value. It is what it is.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Clinical framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>channels.peris.people</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>These were people.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Humane framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>channels.aster.hungry</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>They were. And we're hungry.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pragmatism</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>channels.narration.shelter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>A sealed alcove beside the main flow. The door responds to proximity. Inside: dry, warm, defensible.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Shelter 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>channels.endo.door</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>He opens the door. Steps aside. The same gesture as the junction.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Endo at shelter</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>stacks.narration.enter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>The drainage channels give way to something industrial. Server racks in rows. Cooling systems humming. The sound of computation.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Entering the Processing Stacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>stacks.aster.home</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>I know this infrastructure. These are the processing cores. Every data point I've ever analyzed was processed here.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aster recognizes the hardware</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>stacks.peris.cold</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>It's cold in here. And loud. How does anyone work in this?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Peris in a machine environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stacks.aster.terminal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>There. A maintenance terminal. No friendly interface — just raw logs.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Raw data access</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>stacks.aster.cleaned</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>"The data has been cleaned and normalized to correct for anomalies." The same words. From my desk in the simulation.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Information trail begins</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stacks.aster.here</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>It happened here. On these servers. Through these conduits. The system that gave me the drink machine is the same one that cleaned my reports.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Connecting the dots</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>stacks.peris.ok</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Are you OK?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stacks.aster.not_sure</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>I'm not sure what I expected to find. But it wasn't this.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Processing the betrayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>stacks.narration.elegant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>One section is noticeably better than its surroundings. The cable routing is elegant, almost artistic. Someone who cared about this hardware shaped these rows.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Myke retroactive storytelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stacks.narration.closet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A small workspace between two racks. A half-finished schematic, crossed out and restarted in the margins. Someone was designing something better and kept stopping.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Myke was here</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stacks.aster.archive</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Older data here. The system keeps its own history in layers. I can read backwards through it.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Archive access</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>stacks.aster.when</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The normalization started on a specific date. Someone built the protocol. Someone authorized it. The terminal doesn't say who, but it shows when.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The trail has a beginning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>stacks.peris.meaning</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>What does that mean for us?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>stacks.aster.means</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>It means the data isn't broken. Someone is making it wrong. On purpose.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not failure — policy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rings.narration.enter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>The corridors change. Clean. Lit. Warm. People walk past on their own routines. Simulation bays glow through windows.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Entering the Residential Rings</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rings.aster.signal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>System signals everywhere. Processing stations, transit routing, the full network. This is civilization.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aster reads the infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rings.peris.remember</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>I know this place. My clients lived here. The inner ones.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Peris recognizes territory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rings.peris.hello</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Hello? It... it's me. Peris. From the feed.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tries to connect</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rings.narration.client</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The client looks confused. Recognizes the voice but not the face. They hurry away.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The feed was a wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rings.peris.wall</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The feed was supposed to connect us. It was a wall the whole time.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Peris realizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rings.narration.empty</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Some apartments are empty. The system lists the occupants as "reassigned." Their belongings are still on the shelves.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Disappearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rings.aster.tags</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Our tags are still flagged here. We can see all of this, but we can't participate.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ghosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rings.endo.discomfort</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>He's checking behind them more often. His movements are less fluid. He keeps touching the walls.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Endo far from his wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rings.endo.stops</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>He stops. Looks back. Looks forward. Looks at them. Then turns around.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Endo chooses the wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rings.peris.endo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Endo?</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>rings.narration.leaving</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>He doesn't explain. He's already walking back. His section of the wall needs him.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Endothelial cells don't travel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>rings.peris.understands</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>I understand. Some people can only function in their own space.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Social worker reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rings.aster.just_us</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>So it's just us now.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rings.peris.visiting</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>It's been just us since the elevator. Endo was visiting.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reframe: Endo was the guest</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>lockout.narration.clean</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>The corridors get cleaner. The clicking fades. The air smells filtered. Infrastructure lights improve.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Approaching the boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>lockout.aster.signals</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>System signals are strong here. Processing stations, transit routing. We're close.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Proximity to civilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lockout.aster.panel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Access panel. Standard interface. Let me just...</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aster tries to interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lockout.system.rejected</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NON-COMPLIANT: WELLNESS PROTOCOL DEVIATION. ACCESS REVOKED.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lockout.aster.again</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No. Let me try again.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Denial</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lockout.system.rejected2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ACCESS REVOKED. REPORT TO NEAREST PROCESSING STATION.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Same result</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lockout.aster.hack</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>I can hack it. I hacked the elevator. I can hack this.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brute force attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lockout.system.blocked</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>UNAUTHORIZED ACCESS ATTEMPT LOGGED. RESPONSE UNIT DISPATCHED.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Triggers enforcers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lockout.narration.footsteps</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Coordinated footsteps. The scan-sweep sound. The calm efficiency of units following protocol.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Naturalizers converging</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lockout.peris.run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>We need to go. Now.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lockout.narration.chase</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>They run. The Naturalizers don't. They walk with purpose. The gentle hands from Tag Day are reaching for them.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lockout.narration.boundary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The Naturalizers stop at the boundary where the system's infrastructure ends. They stand. They scan. They wait.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The system does not extend here</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lockout.aster.not_in</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>It's not letting me back in.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The real lockout</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lockout.peris.back_to</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>...Back in to what?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not rhetorical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>lockout.narration.forward</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The Naturalizers watch from the boundary. The clicking of Chelators resumes behind them. There is no going back.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Exile is permanent</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -2897,12 +2897,13 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>tag_day.checkpoint_id</t>
-        </is>
-      </c>
+          <t>tag_day.poem.01</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2912,522 +2913,589 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
+          <t>Between the idea
+And the reality
+Between the motion
+And the act</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Data overlay as Aster arrives at checkpoint</t>
+          <t>First stanza — the gap between intention and action</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Looks like I win the bet. Not weird. He's just babbling like most of them did yesterday.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NK-01 claims victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tag_day.poem.02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>poem</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Falls the Shadow
+For Thine is the Kingdom</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Refrain — the Shadow falls between</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Well, it's weirdly structured, unlike all that gibberish we heard.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NK-02 pushing back</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tag_day.poem.03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>poem</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Between the conception
+And the creation
+Between the emotion
+And the response</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Second stanza — the gap between feeling and acting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>You'll call anything weird, like that case of complete silence.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NK-01 dismissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Silence IS weird. Yet you didn't get that hint last time you tried courtship, did you?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NK-02 pivots to personal jab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tag_day.poem.04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>poem</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Falls the Shadow
+Life is very long</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Refrain — life stretches</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>We had three cases of silence in the last week. It's completely normal.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NK-01 deflecting with statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>...says the guy who spent his date completely silent before getting completely ghosted.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NK-02 lands the kill shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tag_day.poem.05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>poem</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Between the desire
+And the spasm
+Between the potency
+And the existence
+Between the essence
+And the descent</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Third stanza — the full descent, longest breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>I'm working on my approach.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NK-01 retreating to vague self-improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>You've been 'working on your approach' since orientation. How's that going?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NK-02 won't let him have it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tag_day.poem.06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>poem</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Falls the Shadow
+For Thine is the Kingdom</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Final refrain before collapse</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>There's still time.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NK-01 down to bare assertion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Is there? You're what, twenty-three? Twenty-four?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NK-02 names the number — casual and terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tag_day.checkpoint_id</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Data overlay as Aster arrives at checkpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>tag_day.murmur.01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 Prickly pear prickly pear</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Citizen murmuring in queue — nursery rhyme draws attention</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>tag_day.murmur.02</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 At five o'clock in the morning.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Citizen continues in queue before scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tag_day.scan_failed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>STATION 7-B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Citizen's device scan fails</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tag_day.poem.01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Between the idea
-And the reality</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Shadow stanzas begin — corridor walk</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Looks like I win the bet. Not weird. He's just babbling like most of them did yesterday.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NK-01 claims victory — Label3D at ~4s</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tag_day.poem.02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Between the motion
-And the act</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Well, it's weirdly structured, unlike all that gibberish we heard.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NK-02 pushing back — Label3D at ~8s</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tag_day.poem.03</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Falls the Shadow</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tag_day.poem.04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>For Thine is the Kingdom</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>You'll call anything weird, like that case of complete silence.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>NK-01 dismissing — Label3D at ~13s</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tag_day.poem.05</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Between the conception
-And the creation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.04</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Silence IS weird. Yet you didn't get that hint last time you tried courtship, did you?</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NK-02 pivots to personal jab — Label3D at ~18s</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tag_day.poem.06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Between the emotion
-And the response</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.05</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>We had three cases of silence in the last week. It's completely normal.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NK-01 deflecting with statistics — Label3D at ~23s</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tag_day.poem.07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Falls the Shadow</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tag_day.poem.08</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Life is very long</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.06</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>...says the guy who spent his date completely silent before getting completely ghosted.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NK-02 lands the kill shot — Label3D at ~28s</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tag_day.poem.09</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>poem</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Between the desire
-And the spasm</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Voice steady as they walk deeper</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.07</t>
+          <t>tag_day.scan_failed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NK-01</t>
+          <t>STATION 7-B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3437,24 +3505,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I'm working on my approach.</t>
+          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NK-01 retreating to vague self-improvement — Label3D at ~33s</t>
+          <t>Citizen's device scan fails</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tag_day.poem.10</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3464,25 +3533,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Between the potency
-And the existence</t>
+          <t>For Thine is</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Syntax collapsing — fragments of prayer stuttering</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.08</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3492,24 +3561,21 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>You've been 'working on your approach' since orientation. How's that going?</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NK-02 won't let him have it — Label3D at ~38s</t>
-        </is>
-      </c>
+          <t>Life is</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tag_day.poem.11</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3519,25 +3585,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Between the essence
-And the descent</t>
-        </is>
-      </c>
+          <t>For Thine is the</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.09</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3547,24 +3609,21 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>There's still time.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NK-01 down to bare assertion — Label3D at ~43s</t>
-        </is>
-      </c>
+          <t>This is the way the world ends</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tag_day.poem.12</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3574,24 +3633,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falls the Shadow</t>
-        </is>
-      </c>
+          <t>This is the way the world ends</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.10</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3601,24 +3657,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Is there? You're what, twenty-three? Twenty-four?</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NK-02 names the number — casual and terminal — Label3D at ~48s</t>
-        </is>
-      </c>
+          <t>This is the way the world ends</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tag_day.poem.13</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3628,19 +3681,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>For Thine is the Kingdom</t>
+          <t>Not with a BANG...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The final line breaks mid-word</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tag_day.fragment.01</t>
-        </is>
-      </c>
+          <t>tag_day.fragment.08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3650,24 +3709,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>For Thine is</t>
+          <t>...but a whimper.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Syntax collapsing — fragments of prayer stuttering</t>
+          <t>Muffled behind the closed door</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tag_day.fragment.02</t>
-        </is>
-      </c>
+          <t>tag_day.lockdown</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3677,19 +3737,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Life is</t>
+          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lockdown alarm after neutralization</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tag_day.fragment.03</t>
+          <t>tag_day.groan</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BYSTANDER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3699,19 +3769,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>For Thine is the</t>
+          <t>Come on... I need to get back to work.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bystander reacting to the lockdown delay</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tag_day.fragment.04</t>
+          <t>tag_day.report_blocked</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ASTER</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3721,19 +3801,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
+          <t>Ugh, can't even make an incident report.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aster frustrated — device locked during protocol enforcement</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tag_day.fragment.05</t>
+          <t>tag_day.scan_passed</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>STATION 7-B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3743,19 +3833,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
+          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Aster scans clean</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tag_day.fragment.06</t>
-        </is>
-      </c>
+          <t>tag_day.clearance</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3765,214 +3861,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tag_day.fragment.07</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Not with a BANG...</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>The final line breaks mid-word</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>tag_day.fragment.08</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>whisper</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>...but a whimper.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Muffled behind the closed door</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>tag_day.lockdown</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Lockdown alarm after neutralization</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>tag_day.groan</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BYSTANDER</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Come on... I need to get back to work.</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Bystander reacting to the lockdown delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>tag_day.report_blocked</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ASTER</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Ugh, can't even make an incident report.</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Aster frustrated — device locked during protocol enforcement</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>tag_day.scan_passed</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>STATION 7-B</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Aster scans clean</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>tag_day.clearance</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
           <t>Blue light. Clean reading.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Blue clearance — auto-advances into transition</t>
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5229,7 +5133,6 @@
           <t>channels.narration.enter</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5321,7 +5224,6 @@
           <t>channels.endo.stop</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5413,7 +5315,6 @@
           <t>channels.narration.flora</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5537,7 +5438,6 @@
           <t>channels.narration.branch</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5565,7 +5465,6 @@
           <t>channels.endo.point</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5593,7 +5492,6 @@
           <t>channels.narration.body</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5621,7 +5519,6 @@
           <t>channels.endo.kneel</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5777,7 +5674,6 @@
           <t>channels.narration.shelter</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5805,7 +5701,6 @@
           <t>channels.endo.door</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>normal</t>
@@ -5847,7 +5742,6 @@
           <t>stacks.narration.enter</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6055,7 +5949,6 @@
           <t>Are you OK?</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6095,7 +5988,6 @@
           <t>stacks.narration.elegant</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6123,7 +6015,6 @@
           <t>stacks.narration.closet</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6235,7 +6126,6 @@
           <t>What does that mean for us?</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6289,7 +6179,6 @@
           <t>rings.narration.enter</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6413,7 +6302,6 @@
           <t>rings.narration.client</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6473,7 +6361,6 @@
           <t>rings.narration.empty</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6533,7 +6420,6 @@
           <t>rings.endo.discomfort</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6561,7 +6447,6 @@
           <t>rings.endo.stops</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6609,7 +6494,6 @@
           <t>Endo?</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6617,7 +6501,6 @@
           <t>rings.narration.leaving</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>normal</t>
@@ -6697,7 +6580,6 @@
           <t>So it's just us now.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6751,7 +6633,6 @@
           <t>lockout.narration.clean</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" t="inlineStr">
         <is>
           <t>normal</t>
@@ -7003,7 +6884,6 @@
           <t>lockout.narration.footsteps</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>normal</t>
@@ -7051,7 +6931,6 @@
           <t>We need to go. Now.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7059,7 +6938,6 @@
           <t>lockout.narration.chase</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>normal</t>
@@ -7087,7 +6965,6 @@
           <t>lockout.narration.boundary</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>normal</t>
@@ -7179,7 +7056,6 @@
           <t>lockout.narration.forward</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>normal</t>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -2891,27 +2891,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>tag_day.citizen.talk</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>CITIZEN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>It's this time again, huh?</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Citizen tries small talk — the last normal thing they say</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tag_day.aster.shush</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Shh, that's against protocol.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Aster shuts them down — productivity over connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tag_day.citizen.scan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The citizen looks at him for a moment. Then they turn back to the scanner.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The citizen presents their tag. The scan fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>tag_day.poem.01</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Between the idea
 And the reality
@@ -2919,123 +3010,121 @@
 And the act</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>First stanza — the gap between intention and action</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>NK-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Looks like I win the bet. Not weird. He's just babbling like most of them did yesterday.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>NK-01 claims victory</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>tag_day.poem.02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Falls the Shadow
 For Thine is the Kingdom</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Refrain — the Shadow falls between</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.02</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>NK-02</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Well, it's weirdly structured, unlike all that gibberish we heard.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>NK-02 pushing back</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>tag_day.poem.03</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Between the conception
 And the creation
@@ -3043,187 +3132,185 @@
 And the response</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Second stanza — the gap between feeling and acting</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>NK-01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>You'll call anything weird, like that case of complete silence.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>NK-01 dismissing</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.04</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>NK-02</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Silence IS weird. Yet you didn't get that hint last time you tried courtship, did you?</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>NK-02 pivots to personal jab</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>tag_day.poem.04</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Falls the Shadow
 Life is very long</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Refrain — life stretches</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.05</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>NK-01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>We had three cases of silence in the last week. It's completely normal.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>NK-01 deflecting with statistics</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.06</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>NK-02</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>...says the guy who spent his date completely silent before getting completely ghosted.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>NK-02 lands the kill shot</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>tag_day.poem.05</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Between the desire
 And the spasm
@@ -3233,349 +3320,265 @@
 And the descent</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Third stanza — the full descent, longest breath</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.07</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>NK-01</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>I'm working on my approach.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>NK-01 retreating to vague self-improvement</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>tag_day.nk_chat.08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>NK-02</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>You've been 'working on your approach' since orientation. How's that going?</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>NK-02 won't let him have it</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>tag_day.poem.06</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Falls the Shadow
 For Thine is the Kingdom</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Final refrain before collapse</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>There's still time.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NK-01 down to bare assertion</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Is there? You're what, twenty-three? Twenty-four?</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NK-02 names the number — casual and terminal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tag_day.checkpoint_id</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Data overlay as Aster arrives at checkpoint</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>There's still time.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NK-01 down to bare assertion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tag_day.nk_chat.10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Is there? You're what, twenty-three? Twenty-four?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NK-02 names the number — casual and terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tag_day.checkpoint_id</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Data overlay as Aster arrives at checkpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>tag_day.murmur.01</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 Prickly pear prickly pear</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Citizen murmuring in queue — nursery rhyme draws attention</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>tag_day.murmur.02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 At five o'clock in the morning.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Citizen continues in queue before scan</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>tag_day.scan_failed</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>STATION 7-B</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Citizen's device scan fails</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>tag_day.fragment.01</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>For Thine is</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Syntax collapsing — fragments of prayer stuttering</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>tag_day.fragment.02</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Life is</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tag_day.fragment.03</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>tag_day.scan_failed</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>STATION 7-B</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3585,18 +3588,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>For Thine is the</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Citizen's device scan fails</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tag_day.fragment.04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>tag_day.fragment.01</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>fragment</t>
@@ -3609,18 +3615,21 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>For Thine is</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Syntax collapsing — fragments of prayer stuttering</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tag_day.fragment.05</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>tag_day.fragment.02</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>fragment</t>
@@ -3633,18 +3642,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>Life is</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tag_day.fragment.06</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>tag_day.fragment.03</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>fragment</t>
@@ -3657,18 +3664,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>This is the way the world ends</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>For Thine is the</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tag_day.fragment.07</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>tag_day.fragment.04</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>fragment</t>
@@ -3681,25 +3686,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Not with a BANG...</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>The final line breaks mid-word</t>
+          <t>This is the way the world ends</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tag_day.fragment.08</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>tag_day.fragment.05</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3709,25 +3708,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>...but a whimper.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Muffled behind the closed door</t>
+          <t>This is the way the world ends</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tag_day.lockdown</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>tag_day.fragment.06</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3737,29 +3730,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Lockdown alarm after neutralization</t>
+          <t>This is the way the world ends</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tag_day.groan</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BYSTANDER</t>
+          <t>tag_day.fragment.07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3769,29 +3752,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Come on... I need to get back to work.</t>
+          <t>Not with a BANG...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bystander reacting to the lockdown delay</t>
+          <t>The final line breaks mid-word</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tag_day.report_blocked</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ASTER</t>
+          <t>tag_day.fragment.08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3801,24 +3779,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ugh, can't even make an incident report.</t>
+          <t>...but a whimper.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aster frustrated — device locked during protocol enforcement</t>
+          <t>Muffled behind the closed door</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tag_day.scan_passed</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>STATION 7-B</t>
+          <t>tag_day.lockdown</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3833,50 +3806,138 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
+          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster scans clean</t>
+          <t>Lockdown alarm after neutralization</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>tag_day.groan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BYSTANDER</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Come on... I need to get back to work.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bystander reacting to the lockdown delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tag_day.report_blocked</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ASTER</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ugh, can't even make an incident report.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aster frustrated — device locked during protocol enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tag_day.scan_passed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>STATION 7-B</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Aster scans clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>tag_day.clearance</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>Blue light. Clean reading.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Blue clearance — auto-advances into transition</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4330,7 +4391,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aster at the puzzle game — can't fathom leisure_x000d_</t>
+          <t>Aster can't fathom leisure — "Lot Clot" scratched into the base plate</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4418,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oh, it's a little puzzle. Someone made this by hand. It's been used a lot, look how smooth the edges are.</t>
+          <t>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peris at the puzzle game — she sees the care and the loneliness_x000d_</t>
+          <t>Peris sees the care and the years of play — sliding block puzzle about clearing blockages</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -1612,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2344,17 +2344,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>elevator.system.noncompliant</t>
+          <t>elevator.peris.not_supposed</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TAG STATUS: NON-COMPLIANT  //  WELLNESS PROTOCOL DEVIATION</t>
+          <t>I don't think we're supposed to be here.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Notification Aster dismisses — not a lockout yet_x000d_</t>
+          <t>Entering the maintenance corridor_x000d_</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>elevator.aster.dismiss</t>
+          <t>elevator.aster.no_service</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2396,24 +2396,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Administrative error. I'll sort it out when we get back.</t>
+          <t>Nobody is. This section hasn't been serviced in... the maintenance logs just stop.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aster doesn't understand what non-compliant means yet_x000d_</t>
+          <t>Aster reads corridor data_x000d_</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>elevator.peris.not_back</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>elevator.bridge.narration</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2428,24 +2423,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I don't really have anything to go back to, anyways...</t>
+          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open — it smells like rust.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Bridge description_x000d_</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>elevator.aster.forward</t>
+          <t>elevator.peris.bodies</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2460,24 +2455,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Forward then.</t>
+          <t>Those people down there...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>_x000d_</t>
+          <t>Peris sees bodies below the bridge_x000d_</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>elevator.peris.not_supposed</t>
+          <t>elevator.aster.logs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2492,19 +2487,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I don't think we're supposed to be here.</t>
+          <t>All casualties are supposed to be logged. I'll check the records when we find a working terminal. Come on.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Entering the maintenance corridor_x000d_</t>
+          <t>Aster files it as data and keeps moving_x000d_</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>elevator.aster.no_service</t>
+          <t>elevator.aster.ahead</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2514,29 +2509,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nobody is. This section hasn't been serviced in... the maintenance logs just stop.</t>
+          <t>There's something ahead. Lights.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aster reads corridor data_x000d_</t>
+          <t>Waits for click — bridge collapse follows_x000d_</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>elevator.bridge.narration</t>
+          <t>elevator.peris.floor</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2551,19 +2551,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open — it smells like rust.</t>
+          <t>The floor—!</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bridge description_x000d_</t>
+          <t>Bridge gives way_x000d_</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>elevator.peris.bodies</t>
+          <t>elevator.peris.hurt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2583,19 +2583,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Those people down there...</t>
+          <t>Are you hurt?</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peris sees bodies below the bridge_x000d_</t>
+          <t>After the fall_x000d_</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>elevator.aster.logs</t>
+          <t>elevator.aster.sublevel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2615,19 +2615,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>All casualties are supposed to be logged. I'll check the records when we find a working terminal. Come on.</t>
+          <t>Sub-level. We fell through.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster files it as data and keeps moving_x000d_</t>
+          <t>Aster reads the environment_x000d_</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>elevator.aster.ahead</t>
+          <t>elevator.aster.climb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>There's something ahead. Lights.</t>
+          <t>They might have called me a beast, but I'm not this type of animal...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Waits for click — bridge collapse follows_x000d_</t>
+          <t>Looking up at the collapsed bridge — no way back up_x000d_</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>elevator.peris.floor</t>
+          <t>elevator.peris.climb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2679,29 +2679,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The floor—!</t>
+          <t>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bridge gives way_x000d_</t>
+          <t>_x000d_</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>elevator.peris.hurt</t>
+          <t>elevator.aster.another_way</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2711,19 +2711,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Are you hurt?</t>
+          <t>There's something over there. Another way forward.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>After the fall_x000d_</t>
+          <t>Finds the alternative path (TBD)_x000d_</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>elevator.aster.sublevel</t>
+          <t>elevator.aster.two_paths</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2743,138 +2743,10 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sub-level. We fell through.</t>
+          <t>Two corridors. One's clear but corroded. The other's shorter, but something's in there.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>Aster reads the environment_x000d_</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>elevator.aster.climb</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Aster</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>They might have called me a beast, but I'm not this type of animal...</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Looking up at the collapsed bridge — no way back up_x000d_</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>elevator.peris.climb</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Peris</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>elevator.aster.another_way</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Aster</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>There's something over there. Another way forward.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Finds the alternative path (TBD)_x000d_</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>elevator.aster.two_paths</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Aster</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Two corridors. One's clear but corroded. The other's shorter, but something's in there.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
         <is>
           <t>Aster reads the fork — safe route has iron hazards on floor; dangerous route has hostiles</t>
         </is>
@@ -2964,7 +2836,6 @@
           <t>tag_day.citizen.scan</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>normal</t>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -3557,7 +3557,9 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>This is the way the world ends|This is the way the world ends|This is the way the world ends</t>
+          <t>This is the way the world ends
+This is the way the world ends
+This is the way the world ends</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Aster frustrated at desk — model isn't working_x000d_</t>
+          <t>Aster frustrated at desk - model isn't working</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Institutional stonewalling — he's trying to do better work_x000d_</t>
+          <t>Institutional stonewalling - he's trying to do better work</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ron checks his device as he walks up_x000d_</t>
+          <t>Ron checks his device as he walks up</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ron glances at device — read the name off it_x000d_</t>
+          <t>Ron glances at device, reads the name off it</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ron genuinely curious — sets up Aster showing the terminal_x000d_</t>
+          <t>Ron asks Aster about his work</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tutorial beat: player moves Aster to terminal_x000d_</t>
+          <t>Tutorial: player moves Aster to terminal</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Visible on terminal — set dressing now; most important sentence later_x000d_</t>
+          <t>Message on terminal (will be replaced by GUI and other message about crediting support team)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ron tying initiative to perks — institutional carrot_x000d_</t>
+          <t>Ron praises Aster, brings up drink machine</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Label that appears over the drink machine during tutorial_x000d_</t>
+          <t>Label that appears over the drink machine during tutorial</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Soft redirect if player wanders away from drink machine_x000d_</t>
+          <t>Soft redirect if player wanders away from drink machine</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The motto — directive disguised as camaraderie_x000d_</t>
+          <t>"Move fast and break things" but it's broken lol</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TAG VERIFICATION — CHECKPOINT 7-B — REPORT WITHIN 15 MINUTES</t>
+          <t>TAG VERIFICATION // CHECKPOINT 7-B // REPORT WITHIN 15 MINUTES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Device notification_x000d_</t>
+          <t>Device notification</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ron reacts to the device notification_x000d_</t>
+          <t>Ron reacts to the device notification</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Time for Tag Day. Routine.</t>
+          <t>Man, they should really automate these checks sometime...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aster's flat reaction — waits for player click</t>
+          <t>Aster reacts</t>
         </is>
       </c>
     </row>
@@ -914,11 +914,6 @@
           <t>text</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>context_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -943,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Peris at her desk waiting for client_x000d_</t>
+          <t>Peris at her desk waiting for client</t>
         </is>
       </c>
     </row>
@@ -970,12 +965,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sorry I'm late. Sorry. I was — there was someone following me.</t>
+          <t>Sorry I'm late. Sorry. I was... there was someone following me.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monos arrives flustered through the portal_x000d_</t>
+          <t>Monos arrives flustered through the portal</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1002,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trailing off — the fear he didn't lose them_x000d_</t>
+          <t>Trailing off - the fear he didn't lose them</t>
         </is>
       </c>
     </row>
@@ -1037,11 +1032,6 @@
           <t>Anyway. I'm here now. Let's start.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1071,7 +1061,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Session opener — casual warmth_x000d_</t>
+          <t>Session opener - casual warmth</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1093,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monos tired — not elaborating_x000d_</t>
+          <t>Monos tired - not elaborating</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1125,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monos can't relax_x000d_</t>
+          <t>Monos can't relax</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1157,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peris reassuring_x000d_</t>
+          <t>Peris reassuring</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1189,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trying to compose himself_x000d_</t>
+          <t>Trying to compose himself</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1221,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ready to begin the session_x000d_</t>
+          <t>Ready to begin the session</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1248,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>—!</t>
+          <t>...!</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Attack through the portal — Monos is hurt_x000d_</t>
+          <t>Attack through the portal - Monos is hurt</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mandatory compliance warning — not optional_x000d_</t>
+          <t>Mandatory compliance warning - not optional</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1317,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peris's instinct — first ability is care_x000d_</t>
+          <t>Peris's instinct - first ability is care</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1344,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Urgency — player must run to portal_x000d_</t>
+          <t>Urgency - player must run to portal</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1371,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Soft redirect if player ignores Monos — Peris's care ethic_x000d_</t>
+          <t>Soft redirect if player ignores Monos - Peris's care ethic</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1398,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Redirect if player tries ability out of range_x000d_</t>
+          <t>Redirect if player tries ability out of range</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1425,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Player tried to run before queuing protect_x000d_</t>
+          <t>Player tried to run before queuing protect</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1452,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Player clicked somewhere other than near Monos_x000d_</t>
+          <t>Player clicked somewhere other than near Monos</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1479,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Player tried to unpause too early_x000d_</t>
+          <t>Player tried to unpause too early</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1501,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wait — I need to queue the ability first.</t>
+          <t>Wait... I need to queue the ability first.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Player tried to unpause before queuing protect_x000d_</t>
+          <t>Player tried to unpause before queuing protect</t>
         </is>
       </c>
     </row>
@@ -1546,11 +1536,6 @@
           <t>I... thank you. I don't know what that was. Thank you, Peris.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1575,12 +1560,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SESSION COMPLETE — EFFICIENCY: 62%  //  OVERTIME PENALTY LOGGED</t>
+          <t>SESSION COMPLETE // EFFICIENCY: 62% // OVERTIME PENALTY LOGGED</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Efficiency penalty_x000d_</t>
+          <t>Efficiency penalty</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1582,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Session ends — portal closes and Monos fades out</t>
+          <t>Session ends - portal closes and Monos fades out</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1628,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Peris wakes in the elevator_x000d_</t>
+          <t>Peris wakes in the elevator</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1655,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scene description_x000d_</t>
+          <t>Scene description</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1687,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris approaches Aster_x000d_</t>
+          <t>Peris approaches Aster</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1719,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aster wakes groggy — still in the simulation mentally_x000d_</t>
+          <t>Aster wakes groggy - still in the simulation mentally</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1751,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aster realizes_x000d_</t>
+          <t>Aster realizes</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1783,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aster checks device first thing_x000d_</t>
+          <t>Aster checks device first thing</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1815,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peris confirms they're stuck_x000d_</t>
+          <t>Peris confirms they're stuck</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1845,6 @@
           <t>Why are we here?</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1894,7 +1874,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aster retells it flatly — doesn't know what happened_x000d_</t>
+          <t>Aster retells it flatly - doesn't know what happened</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1906,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No mention of the bang — Aster's data view couldn't see the room_x000d_</t>
+          <t>No mention of the bang - Aster's data view couldn't see the room</t>
         </is>
       </c>
     </row>
@@ -1956,11 +1936,6 @@
           <t>Is he OK?</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1990,7 +1965,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cites the policy like it settles the matter_x000d_</t>
+          <t>Cites the policy like it settles the matter</t>
         </is>
       </c>
     </row>
@@ -2022,7 +1997,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pivots — policy is also what happened to her_x000d_</t>
+          <t>Pivots - policy is also what happened to her</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2029,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peris disturbed by how soothing it was meant to be_x000d_</t>
+          <t>Peris disturbed by how soothing it was meant to be</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2061,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oblivious flex — interrupted by system restoration_x000d_</t>
+          <t>Oblivious flex - interrupted by system restoration</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2093,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>System restores devices and wakes escorts simultaneously_x000d_</t>
+          <t>System restores devices and wakes escorts simultaneously</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2125,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aster's data overlay reveals the panel_x000d_</t>
+          <t>Aster's data overlay reveals the panel</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2157,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Escort units activate as part of the same restoration_x000d_</t>
+          <t>Escort units activate as part of the same restoration</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2189,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aster panicking but finding a solution_x000d_</t>
+          <t>Aster panicking but finding a solution</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2221,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Post-EMP urgency_x000d_</t>
+          <t>Post-EMP urgency</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2253,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aster begins hacking the panel_x000d_</t>
+          <t>Aster begins hacking the panel</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2285,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hack succeeds_x000d_</t>
+          <t>Hack succeeds</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2312,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doors open_x000d_</t>
+          <t>Doors open</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2344,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entering the maintenance corridor_x000d_</t>
+          <t>Entering the maintenance corridor</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2376,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aster reads corridor data_x000d_</t>
+          <t>Aster reads corridor data</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2398,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open — it smells like rust.</t>
+          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open -- it smells like rust.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bridge description_x000d_</t>
+          <t>Bridge description</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2435,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peris sees bodies below the bridge_x000d_</t>
+          <t>Peris sees bodies below the bridge</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2467,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aster files it as data and keeps moving_x000d_</t>
+          <t>Aster files it as data and keeps moving</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2499,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waits for click — bridge collapse follows_x000d_</t>
+          <t>Waits for click - bridge collapse follows</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2526,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The floor—!</t>
+          <t>The floor...!</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bridge gives way_x000d_</t>
+          <t>Bridge gives way</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2563,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>After the fall_x000d_</t>
+          <t>After the fall</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2595,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster reads the environment_x000d_</t>
+          <t>Aster reads the environment</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2627,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Looking up at the collapsed bridge — no way back up_x000d_</t>
+          <t>Looking up at the collapsed bridge - no way back up</t>
         </is>
       </c>
     </row>
@@ -2682,11 +2657,6 @@
           <t>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2716,7 +2686,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finds the alternative path (TBD)_x000d_</t>
+          <t>Finds the alternative path (TBD)</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2718,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aster reads the fork — safe route has iron hazards on floor; dangerous route has hostiles</t>
+          <t>Aster reads the fork - safe route has iron hazards on floor; dangerous route has hostiles</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2764,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Citizen tries small talk — the last normal thing they say</t>
+          <t>Citizen tries small talk - the last normal thing they say</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2796,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster shuts them down — productivity over connection</t>
+          <t>Aster shuts them down - productivity over connection</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2853,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>First stanza — the gap between intention and action</t>
+          <t>First stanza - the gap between intention and action</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2913,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Refrain — the Shadow falls between</t>
+          <t>Refrain - the Shadow falls between</t>
         </is>
       </c>
     </row>
@@ -3005,7 +2975,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Second stanza — the gap between feeling and acting</t>
+          <t>Second stanza - the gap between feeling and acting</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3067,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Refrain — life stretches</t>
+          <t>Refrain - life stretches</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3163,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Third stanza — the full descent, longest breath</t>
+          <t>Third stanza - the full descent, longest breath</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3319,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NK-02 names the number — casual and terminal</t>
+          <t>NK-02 names the number - casual and terminal</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3374,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Citizen murmuring in queue — nursery rhyme draws attention</t>
+          <t>Citizen murmuring in queue - nursery rhyme draws attention</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3461,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Syntax collapsing — fragments of prayer stuttering</t>
+          <t>Syntax collapsing - fragments of prayer stuttering</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3674,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster frustrated — device locked during protocol enforcement</t>
+          <t>Aster frustrated - device locked during protocol enforcement</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3733,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blue clearance — auto-advances into transition</t>
+          <t>Blue clearance - auto-advances into transition</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3774,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Scripted dusk — first nightfall approaching_x000d_</t>
+          <t>Scripted dusk - first nightfall approaching</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3806,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster examines the workbench_x000d_</t>
+          <t>Aster examines the workbench</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3838,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris examines the workbench_x000d_</t>
+          <t>Peris examines the workbench</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3870,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aster reads the monitoring station_x000d_</t>
+          <t>Aster reads the monitoring station</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3902,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Peris reads the monitoring station_x000d_</t>
+          <t>Peris reads the monitoring station</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3934,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aster at the food cache — compliance over survival_x000d_</t>
+          <t>Aster at the food cache - compliance over survival</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3966,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peris at the food cache — empathy over survival_x000d_</t>
+          <t>Peris at the food cache - empathy over survival</t>
         </is>
       </c>
     </row>
@@ -4028,7 +3998,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aster at the lookout spot_x000d_</t>
+          <t>Aster at the lookout spot</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4030,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peris at the lookout spot_x000d_</t>
+          <t>Peris at the lookout spot</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4062,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aster at the heater — data without emotional inference_x000d_</t>
+          <t>Aster at the heater - data without emotional inference</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4094,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Peris at the heater — she reads the care_x000d_</t>
+          <t>Peris at the heater - she reads the care</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aster at the wall markings — unrecognized system_x000d_</t>
+          <t>Aster at the wall markings - unrecognized system</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4158,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Peris at the wall markings — she reads the person_x000d_</t>
+          <t>Peris at the wall markings - she reads the person</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aster can't fathom leisure — "Lot Clot" scratched into the base plate</t>
+          <t>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4222,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peris sees the care and the years of play — sliding block puzzle about clearing blockages</t>
+          <t>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4249,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Endo gestures them inside — marker appears on shelter_x000d_</t>
+          <t>Endo gestures them inside - marker appears on shelter</t>
         </is>
       </c>
     </row>
@@ -4309,11 +4279,6 @@
           <t>Who...?</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4343,7 +4308,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aster scans Endo_x000d_</t>
+          <t>Aster scans Endo</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4335,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Endo offers drink — marker on container_x000d_</t>
+          <t>Endo offers drink - marker on container</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4367,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Accepts the drink_x000d_</t>
+          <t>Accepts the drink</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4394,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Endo takes watch — no marker needed_x000d_</t>
+          <t>Endo takes watch - no marker needed</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4421,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pairs of eyes outside — the player sees them too_x000d_</t>
+          <t>Pairs of eyes outside - the player sees them too</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4448,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The eyes recede with the light_x000d_</t>
+          <t>The eyes recede with the light</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4475,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Evidence of the night visitors_x000d_</t>
+          <t>Evidence of the night visitors</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4507,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aster tries his device — locked out of the simulation_x000d_</t>
+          <t>Aster tries his device - locked out of the simulation</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4539,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Not rhetorical — what exactly does he want to go back to_x000d_</t>
+          <t>Not rhetorical - what exactly does he want to go back to</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4566,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Endo gestures: he's coming with_x000d_</t>
+          <t>Endo gestures: he's coming with</t>
         </is>
       </c>
     </row>
@@ -4631,11 +4596,6 @@
           <t>I think he's coming with us.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4663,11 +4623,6 @@
           <t>I don't see why not.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>_x000d_</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4697,7 +4652,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aster reads the gauntlet_x000d_</t>
+          <t>Aster reads the gauntlet</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4679,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>There's something on the wall. Iron lure — ferrolure. If I activate it, they might go for that instead.</t>
+          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peris recognizes the device_x000d_</t>
+          <t>Peris recognizes the device</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4765,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Endo joins — no words</t>
+          <t>Endo joins - no words</t>
         </is>
       </c>
     </row>
@@ -4832,12 +4787,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>He points ahead. Then at a marker on the wall — a shelter symbol.</t>
+          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Endo gestures toward shelter — marker appears</t>
+          <t>Endo gestures toward shelter - marker appears</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4819,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Endo blocks the iron path — marker on safe route</t>
+          <t>Endo blocks the iron path - marker on safe route</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4846,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Endo notices dusk — urgency without words</t>
+          <t>Endo notices dusk - urgency without words</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4927,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Endo takes watch — same posture as junction</t>
+          <t>Endo takes watch - same posture as junction</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4954,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Morning — waits for click</t>
+          <t>Morning - waits for click</t>
         </is>
       </c>
     </row>
@@ -5035,7 +4990,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The corridor opens. Water runs along the floor in shallow channels. The air is different here — cleaner where the water flows, stale where it pools.</t>
+          <t>The corridor opens. Water runs along the floor in shallow channels. The air is different here -- cleaner where the water flows, stale where it pools.</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -5421,7 +5376,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>He kneels beside the body. A brief pause. Then his hands move — practiced, efficient. He stands with something in his palm.</t>
+          <t>He kneels beside the body. A brief pause. Then his hands move -- practiced, efficient. He stands with something in his palm.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5740,7 +5695,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>There. A maintenance terminal. No friendly interface — just raw logs.</t>
+          <t>There. A maintenance terminal. No friendly interface -- just raw logs.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6045,7 +6000,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not failure — policy</t>
+          <t>Not failure - policy</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -3748,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4482,12 +4482,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>junction.aster.back_in</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>junction.endo.stands</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4502,19 +4497,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>It's not letting me back in.</t>
+          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aster tries his device - locked out of the simulation</t>
+          <t>Endo gestures: he's coming with</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>junction.peris.back_to_what</t>
+          <t>junction.peris.coming</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4534,19 +4529,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>...Back in to what?</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Not rhetorical - what exactly does he want to go back to</t>
+          <t>I think he's coming with us.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>junction.endo.stands</t>
+          <t>junction.aster.ok</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4561,29 +4556,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Endo gestures: he's coming with</t>
+          <t>I don't see why not.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>junction.peris.coming</t>
+          <t>junction.aster.blocked</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4593,19 +4583,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I think he's coming with us.</t>
+          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Aster reads the gauntlet</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>junction.aster.ok</t>
+          <t>junction.peris.ferrolure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4620,19 +4615,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I don't see why not.</t>
+          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Peris recognizes the device</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>junction.aster.blocked</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>junction.ferrolure.active</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4647,24 +4642,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
+          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aster reads the gauntlet</t>
+          <t>System readout</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>junction.peris.ferrolure</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.exit_narration</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4679,24 +4669,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
+          <t>The facility door seals behind you. The corridor stretches ahead.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Peris recognizes the device</t>
+          <t>Leaving the facility</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>junction.ferrolure.active</t>
+          <t>junction.endo_appears</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4706,19 +4696,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
+          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>System readout</t>
+          <t>Endo joins - no words</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>junction.exit_narration</t>
+          <t>junction.endo.shelters</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4733,19 +4723,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The facility door seals behind you. The corridor stretches ahead.</t>
+          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leaving the facility</t>
+          <t>Endo gestures toward shelter - marker appears</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>junction.endo_appears</t>
+          <t>junction.endo.iron_warn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4760,19 +4750,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
+          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Endo joins - no words</t>
+          <t>Endo blocks the iron path - marker on safe route</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>junction.endo.shelters</t>
+          <t>junction.endo.dusk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4787,19 +4777,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
+          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Endo gestures toward shelter - marker appears</t>
+          <t>Endo notices dusk - urgency without words</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>junction.endo.iron_warn</t>
+          <t>junction.endo.shelter</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4814,19 +4804,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
+          <t>He stops at a door. Opens it. Steps aside.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Endo blocks the iron path - marker on safe route</t>
+          <t>Endo at the shelter entrance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>junction.endo.dusk</t>
+          <t>junction.night_narration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4841,19 +4831,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
+          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Endo notices dusk - urgency without words</t>
+          <t>First night</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>junction.endo.shelter</t>
+          <t>junction.endo.rest</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4868,91 +4858,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>He stops at a door. Opens it. Steps aside.</t>
+          <t>He settles against the wall. Watches the door.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Endo at the shelter entrance</t>
+          <t>Endo takes watch - same posture as junction</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>junction.night_narration</t>
+          <t>junction.dawn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
+          <t>Day 2. Dawn.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
-        <is>
-          <t>First night</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>junction.endo.rest</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>He settles against the wall. Watches the door.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Endo takes watch - same posture as junction</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>junction.dawn</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Day 2. Dawn.</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
         <is>
           <t>Morning - waits for click</t>
         </is>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -453,40 +453,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>aster_sim.working.thought.01</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Ugh, my monitoring model's off again...</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Aster frustrated at desk - model isn't working</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aster_sim.working.thought.02</t>
+          <t>aster_sim.working.thought.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,29 +506,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>They keep complaining about just patching things, yet nobody wants to approve my historical data access requests...</t>
+          <t>Ugh, my monitoring model's off again...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Institutional stonewalling - he's trying to do better work</t>
+          <t>Aster frustrated at desk - model isn't working</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aster_sim.ron.greeting</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ron</t>
+          <t>aster_sim.working.thought.02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,19 +533,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hey hey, star of databank 534b!</t>
+          <t>They keep complaining about just patching things, yet nobody wants to approve my historical data access requests...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ron checks his device as he walks up</t>
+          <t>Institutional stonewalling - he's trying to do better work</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aster_sim.ron.name</t>
+          <t>aster_sim.ron.greeting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -565,19 +565,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aster! Your metrics this quarter are disgusting, you beast.</t>
+          <t>Hey hey, star of databank 534b!</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ron glances at device, reads the name off it</t>
+          <t>Ron checks his device as he walks up</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aster_sim.ron.working_on</t>
+          <t>aster_sim.ron.name</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -597,24 +597,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>What's the big man working on now?</t>
+          <t>Aster! Your metrics this quarter are disgusting, you beast.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ron asks Aster about his work</t>
+          <t>Ron glances at device, reads the name off it</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aster_sim.aster.show</t>
+          <t>aster_sim.ron.working_on</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -629,24 +629,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Here, let me show you.</t>
+          <t>What's the big man working on now?</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tutorial: player moves Aster to terminal</t>
+          <t>Ron asks Aster about his work</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aster_sim.system.cleaned</t>
+          <t>aster_sim.aster.show</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,29 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The data has been cleaned and normalized to correct for anomalies. No further analysis is necessary.</t>
+          <t>Here, let me show you.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Message on terminal (will be replaced by GUI and other message about crediting support team)</t>
+          <t>Tutorial: player moves Aster to terminal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aster_sim.ron.drinks</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ron</t>
+          <t>aster_sim.system.cleaned</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,24 +688,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>That's what I like to see! Exactly the type of thinking that gets perks and no backbreaking manual labor. Speaking of which, enjoy the new drink machine! Unlimited, as always, for top performers like you.</t>
+          <t>The data has been cleaned and normalized to correct for anomalies. No further analysis is necessary.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ron praises Aster, brings up drink machine</t>
+          <t>Message on terminal (will be replaced by GUI and other message about crediting support team)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>aster_sim.drink_label</t>
+          <t>aster_sim.ron.drinks</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -715,24 +720,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>click</t>
+          <t>That's what I like to see! Exactly the type of thinking that gets perks and no backbreaking manual labor. Speaking of which, enjoy the new drink machine! Unlimited, as always, for top performers like you.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Label that appears over the drink machine during tutorial</t>
+          <t>Ron praises Aster, brings up drink machine</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aster_sim.drink_redirect.thought</t>
+          <t>aster_sim.drink_label</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>thought</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -742,29 +747,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I should grab a drink first. I always grab a drink first.</t>
+          <t>click</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Soft redirect if player wanders away from drink machine</t>
+          <t>Label that appears over the drink machine during tutorial</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aster_sim.ron.move_fast</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ron</t>
+          <t>aster_sim.drink_redirect.thought</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>thought</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -774,29 +774,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Keep it up! Move fast and break, am I right?</t>
+          <t>I should grab a drink first. I always grab a drink first.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>"Move fast and break things" but it's broken lol</t>
+          <t>Soft redirect if player wanders away from drink machine</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aster_sim.device.tag_verify</t>
+          <t>aster_sim.ron.move_fast</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -806,29 +806,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TAG VERIFICATION // CHECKPOINT 7-B // REPORT WITHIN 15 MINUTES</t>
+          <t>Keep it up! Move fast and break, am I right?</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Device notification</t>
+          <t>"Move fast and break things" but it's broken lol</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aster_sim.ron.tag_notify</t>
+          <t>aster_sim.device.tag_verify</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>DEVICE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -838,37 +838,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ah, sorry to have to pull you out. You're on a roll!</t>
+          <t>TAG VERIFICATION // CHECKPOINT 7-B // REPORT WITHIN 15 MINUTES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ron reacts to the device notification</t>
+          <t>Device notification</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>aster_sim.ron.tag_notify</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ah, sorry to have to pull you out. You're on a roll!</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ron reacts to the device notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>aster_sim.tag_routine</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Man, they should really automate these checks sometime...</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Aster reacts</t>
         </is>
@@ -914,6 +946,11 @@
           <t>text</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1597,45 +1634,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>elevator.peris.where</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Where...? What is this place?</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Peris wakes in the elevator</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elevator.narration.room</t>
+          <t>elevator.peris.where</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1650,24 +1692,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A small room. Metal walls. Red emergency light cycling overhead. Two white figures against the far wall, dormant. Someone slumped in the corner.</t>
+          <t>Where...? What is this place?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scene description</t>
+          <t>Peris wakes in the elevator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elevator.peris.hey</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>elevator.narration.room</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1682,24 +1719,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hey. Hey, can you hear me? Are you alive? Please be alive.</t>
+          <t>A small room. Metal walls. Red emergency light cycling overhead. Two white figures against the far wall, dormant. Someone slumped in the corner.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris approaches Aster</t>
+          <t>Scene description</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elevator.aster.waking</t>
+          <t>elevator.peris.hey</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,19 +1751,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>...I already submitted the forecast. Check the terminal.</t>
+          <t>Hey. Hey, can you hear me? Are you alive? Please be alive.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aster wakes groggy - still in the simulation mentally</t>
+          <t>Peris approaches Aster</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elevator.aster.where</t>
+          <t>elevator.aster.waking</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1746,19 +1783,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>...This isn't the sim. Where are we?</t>
+          <t>...I already submitted the forecast. Check the terminal.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aster realizes</t>
+          <t>Aster wakes groggy - still in the simulation mentally</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elevator.aster.device_locked</t>
+          <t>elevator.aster.where</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1768,7 +1805,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1778,29 +1815,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>My device is locked. No facility access. No maintenance overlay.</t>
+          <t>...This isn't the sim. Where are we?</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aster checks device first thing</t>
+          <t>Aster realizes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elevator.peris.trapped</t>
+          <t>elevator.aster.device_locked</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1810,19 +1847,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doors won't respond. I tried.</t>
+          <t>My device is locked. No facility access. No maintenance overlay.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peris confirms they're stuck</t>
+          <t>Aster checks device first thing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elevator.peris.why</t>
+          <t>elevator.peris.trapped</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1842,19 +1879,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Why are we here?</t>
+          <t>Doors won't respond. I tried.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Peris confirms they're stuck</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>elevator.aster.wellness</t>
+          <t>elevator.peris.why</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1869,19 +1911,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tag Day. A citizen's scan failed and they walked him to the Wellness Wing.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Aster retells it flatly - doesn't know what happened</t>
+          <t>Why are we here?</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>elevator.aster.singing</t>
+          <t>elevator.aster.wellness</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1901,24 +1938,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>He was reciting something on the way. I couldn't make it out. Then the checkpoint reset.</t>
+          <t>Tag Day. A citizen's scan failed and they walked him to the Wellness Wing.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>No mention of the bang - Aster's data view couldn't see the room</t>
+          <t>Aster retells it flatly - doesn't know what happened</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>elevator.peris.citizen_ok</t>
+          <t>elevator.aster.singing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1933,19 +1970,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Is he OK?</t>
+          <t>He was reciting something on the way. I couldn't make it out. Then the checkpoint reset.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No mention of the bang - Aster's data view couldn't see the room</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>elevator.aster.privacy</t>
+          <t>elevator.peris.citizen_ok</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1960,24 +2002,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I... never thought to ask. It wasn't really any of my business. There's a privacy policy.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Cites the policy like it settles the matter</t>
+          <t>Is he OK?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>elevator.peris.speaking_of</t>
+          <t>elevator.aster.privacy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1992,19 +2029,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Speaking of policy...</t>
+          <t>I... never thought to ask. It wasn't really any of my business. There's a privacy policy.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pivots - policy is also what happened to her</t>
+          <t>Cites the policy like it settles the matter</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>elevator.peris.gel</t>
+          <t>elevator.peris.speaking_of</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2024,24 +2061,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Have you ever performed so poorly they started showing you animations of soap being cut and gel being squished? It's the most uncomfortable comfort I've ever felt.</t>
+          <t>Speaking of policy...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peris disturbed by how soothing it was meant to be</t>
+          <t>Pivots - policy is also what happened to her</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>elevator.aster.perks</t>
+          <t>elevator.peris.gel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2056,29 +2093,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Poorly? I've only performed so well that they give me perks, like this upgraded device...</t>
+          <t>Have you ever performed so poorly they started showing you animations of soap being cut and gel being squished? It's the most uncomfortable comfort I've ever felt.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oblivious flex - interrupted by system restoration</t>
+          <t>Peris disturbed by how soothing it was meant to be</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>elevator.system.restored</t>
+          <t>elevator.aster.perks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2088,29 +2125,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MAINTENANCE CYCLE COMPLETE  //  DEVICE ACCESS RESTORED  //  RESUMING PASSENGER PROTOCOL</t>
+          <t>Poorly? I've only performed so well that they give me perks, like this upgraded device...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>System restores devices and wakes escorts simultaneously</t>
+          <t>Oblivious flex - interrupted by system restoration</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>elevator.aster.overlay</t>
+          <t>elevator.system.restored</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2120,29 +2157,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>My device. It's back. There's a maintenance panel behind the doors.</t>
+          <t>MAINTENANCE CYCLE COMPLETE  //  DEVICE ACCESS RESTORED  //  RESUMING PASSENGER PROTOCOL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aster's data overlay reveals the panel</t>
+          <t>System restores devices and wakes escorts simultaneously</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>elevator.unit.protocol</t>
+          <t>elevator.aster.overlay</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EU-1</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2152,29 +2189,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PASSENGERS CONSCIOUS  //  DISTRESS DETECTED  //  INITIATING RE-SEDATION PROTOCOL</t>
+          <t>My device. It's back. There's a maintenance panel behind the doors.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Escort units activate as part of the same restoration</t>
+          <t>Aster's data overlay reveals the panel</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>elevator.aster.device</t>
+          <t>elevator.unit.protocol</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>EU-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2184,19 +2221,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No no no. My device. I can pulse it, fry their circuits.</t>
+          <t>PASSENGERS CONSCIOUS  //  DISTRESS DETECTED  //  INITIATING RE-SEDATION PROTOCOL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aster panicking but finding a solution</t>
+          <t>Escort units activate as part of the same restoration</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>elevator.aster.stay_close</t>
+          <t>elevator.aster.device</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2216,19 +2253,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>They'll reboot. We don't have long. That panel. Now.</t>
+          <t>No no no. My device. I can pulse it, fry their circuits.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Post-EMP urgency</t>
+          <t>Aster panicking but finding a solution</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>elevator.aster.hack</t>
+          <t>elevator.aster.stay_close</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2248,29 +2285,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I can override this. Just need a moment...</t>
+          <t>They'll reboot. We don't have long. That panel. Now.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aster begins hacking the panel</t>
+          <t>Post-EMP urgency</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>elevator.system.override</t>
+          <t>elevator.aster.hack</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2280,24 +2317,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MAINTENANCE OVERRIDE ACCEPTED  //  DOORS CYCLING</t>
+          <t>I can override this. Just need a moment...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hack succeeds</t>
+          <t>Aster begins hacking the panel</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>elevator.narration.doors</t>
+          <t>elevator.system.override</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2307,24 +2349,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The elevator shudders. The doors grind open. Light spills in from a corridor neither of them recognizes.</t>
+          <t>MAINTENANCE OVERRIDE ACCEPTED  //  DOORS CYCLING</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doors open</t>
+          <t>Hack succeeds</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>elevator.peris.not_supposed</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>elevator.narration.doors</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2339,29 +2376,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I don't think we're supposed to be here.</t>
+          <t>The elevator shudders. The doors grind open. Light spills in from a corridor neither of them recognizes.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entering the maintenance corridor</t>
+          <t>Doors open</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>elevator.aster.no_service</t>
+          <t>elevator.peris.not_supposed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2371,24 +2408,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nobody is. This section hasn't been serviced in... the maintenance logs just stop.</t>
+          <t>I don't think we're supposed to be here.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aster reads corridor data</t>
+          <t>Entering the maintenance corridor</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>elevator.bridge.narration</t>
+          <t>elevator.aster.no_service</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2398,24 +2440,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open -- it smells like rust.</t>
+          <t>Nobody is. This section hasn't been serviced in... the maintenance logs just stop.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bridge description</t>
+          <t>Aster reads corridor data</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>elevator.peris.bodies</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>elevator.bridge.narration</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2430,24 +2467,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Those people down there...</t>
+          <t>An elevated walkway spanning a larger space. Incomplete railing. Exposed framework. The air is open -- it smells like rust.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Peris sees bodies below the bridge</t>
+          <t>Bridge description</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>elevator.aster.logs</t>
+          <t>elevator.peris.bodies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2462,19 +2499,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>All casualties are supposed to be logged. I'll check the records when we find a working terminal. Come on.</t>
+          <t>Those people down there...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aster files it as data and keeps moving</t>
+          <t>Peris sees bodies below the bridge</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>elevator.aster.ahead</t>
+          <t>elevator.aster.logs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2489,29 +2526,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>There's something ahead. Lights.</t>
+          <t>All casualties are supposed to be logged. I'll check the records when we find a working terminal. Come on.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waits for click - bridge collapse follows</t>
+          <t>Aster files it as data and keeps moving</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>elevator.peris.floor</t>
+          <t>elevator.aster.ahead</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2521,24 +2558,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The floor...!</t>
+          <t>There's something ahead. Lights.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bridge gives way</t>
+          <t>Waits for click - bridge collapse follows</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>elevator.peris.hurt</t>
+          <t>elevator.peris.floor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2558,29 +2595,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Are you hurt?</t>
+          <t>The floor...!</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>After the fall</t>
+          <t>Bridge gives way</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>elevator.aster.sublevel</t>
+          <t>elevator.peris.hurt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2590,19 +2627,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sub-level. We fell through.</t>
+          <t>Are you hurt?</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster reads the environment</t>
+          <t>After the fall</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>elevator.aster.climb</t>
+          <t>elevator.aster.sublevel</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2612,7 +2649,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2622,24 +2659,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>They might have called me a beast, but I'm not this type of animal...</t>
+          <t>Sub-level. We fell through.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Looking up at the collapsed bridge - no way back up</t>
+          <t>Aster reads the environment</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>elevator.peris.climb</t>
+          <t>elevator.aster.climb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2654,24 +2691,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</t>
+          <t>They might have called me a beast, but I'm not this type of animal...</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Looking up at the collapsed bridge - no way back up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>elevator.aster.another_way</t>
+          <t>elevator.peris.climb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2681,42 +2723,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>There's something over there. Another way forward.</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Finds the alternative path (TBD)</t>
+          <t>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>elevator.aster.another_way</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>There's something over there. Another way forward.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Finds the alternative path (TBD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>elevator.aster.two_paths</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Aster</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Two corridors. One's clear but corroded. The other's shorter, but something's in there.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Aster reads the fork - safe route has iron hazards on floor; dangerous route has hostiles</t>
         </is>
@@ -2733,50 +2802,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>tag_day.citizen.talk</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CITIZEN</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>It's this time again, huh?</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Citizen tries small talk - the last normal thing they say</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tag_day.aster.shush</t>
+          <t>tag_day.citizen.talk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>CITIZEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2791,19 +2860,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shh, that's against protocol.</t>
+          <t>It's this time again, huh?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster shuts them down - productivity over connection</t>
+          <t>Citizen tries small talk - the last normal thing they say</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tag_day.citizen.scan</t>
+          <t>tag_day.aster.shush</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2818,32 +2892,59 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The citizen looks at him for a moment. Then they turn back to the scanner.</t>
+          <t>Shh, that's against protocol.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The citizen presents their tag. The scan fails.</t>
+          <t>Aster shuts them down - productivity over connection</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>tag_day.citizen.scan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The citizen looks at him for a moment. Then they turn back to the scanner.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The citizen presents their tag. The scan fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>tag_day.poem.01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Between the idea
 And the reality
@@ -2851,121 +2952,121 @@
 And the act</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>First stanza - the gap between intention and action</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Looks like I win the bet. Not weird. He's just babbling like most of them did yesterday.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NK-01 claims victory</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NK-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Looks like I win the bet. Not weird. He's just babbling like most of them did yesterday.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NK-01 claims victory</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>tag_day.poem.02</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Falls the Shadow
 For Thine is the Kingdom</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Refrain - the Shadow falls between</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NK-02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Well, it's weirdly structured, unlike all that gibberish we heard.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NK-02 pushing back</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Well, it's weirdly structured, unlike all that gibberish we heard.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NK-02 pushing back</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>tag_day.poem.03</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Between the conception
 And the creation
@@ -2973,53 +3074,21 @@
 And the response</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Second stanza - the gap between feeling and acting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.03</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>You'll call anything weird, like that case of complete silence.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NK-01 dismissing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.04</t>
+          <t>tag_day.nk_chat.03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NK-02</t>
+          <t>NK-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3034,84 +3103,84 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Silence IS weird. Yet you didn't get that hint last time you tried courtship, did you?</t>
+          <t>You'll call anything weird, like that case of complete silence.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NK-02 pivots to personal jab</t>
+          <t>NK-01 dismissing</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Silence IS weird. Yet you didn't get that hint last time you tried courtship, did you?</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NK-02 pivots to personal jab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>tag_day.poem.04</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Falls the Shadow
 Life is very long</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Refrain - life stretches</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>We had three cases of silence in the last week. It's completely normal.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>NK-01 deflecting with statistics</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.06</t>
+          <t>tag_day.nk_chat.05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NK-02</t>
+          <t>NK-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3126,32 +3195,64 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>...says the guy who spent his date completely silent before getting completely ghosted.</t>
+          <t>We had three cases of silence in the last week. It's completely normal.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NK-02 lands the kill shot</t>
+          <t>NK-01 deflecting with statistics</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>...says the guy who spent his date completely silent before getting completely ghosted.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NK-02 lands the kill shot</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>tag_day.poem.05</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Between the desire
 And the spasm
@@ -3161,53 +3262,21 @@
 And the descent</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Third stanza - the full descent, longest breath</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>I'm working on my approach.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NK-01 retreating to vague self-improvement</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.08</t>
+          <t>tag_day.nk_chat.07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NK-02</t>
+          <t>NK-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3222,84 +3291,84 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>You've been 'working on your approach' since orientation. How's that going?</t>
+          <t>I'm working on my approach.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NK-02 won't let him have it</t>
+          <t>NK-01 retreating to vague self-improvement</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>tag_day.nk_chat.08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NK-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>You've been 'working on your approach' since orientation. How's that going?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NK-02 won't let him have it</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>tag_day.poem.06</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Falls the Shadow
 For Thine is the Kingdom</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Final refrain before collapse</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tag_day.nk_chat.09</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NK-01</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>There's still time.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NK-01 down to bare assertion</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tag_day.nk_chat.10</t>
+          <t>tag_day.nk_chat.09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NK-02</t>
+          <t>NK-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3314,24 +3383,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Is there? You're what, twenty-three? Twenty-four?</t>
+          <t>There's still time.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NK-02 names the number - casual and terminal</t>
+          <t>NK-01 down to bare assertion</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tag_day.checkpoint_id</t>
+          <t>tag_day.nk_chat.10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NK-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3341,112 +3415,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
+          <t>Is there? You're what, twenty-three? Twenty-four?</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Data overlay as Aster arrives at checkpoint</t>
+          <t>NK-02 names the number - casual and terminal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>tag_day.checkpoint_id</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CHECKPOINT 7-B  //  IMMUNITY VERIFICATION</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Data overlay as Aster arrives at checkpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>tag_day.murmur.01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 Prickly pear prickly pear</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Citizen murmuring in queue - nursery rhyme draws attention</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>tag_day.murmur.02</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>poem</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Here we go round the prickly pear
 At five o'clock in the morning.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Citizen continues in queue before scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>tag_day.scan_failed</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>STATION 7-B</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Citizen's device scan fails</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tag_day.fragment.01</t>
+          <t>tag_day.scan_failed</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>STATION 7-B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3456,19 +3530,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>For Thine is</t>
+          <t>SCAN FAILED  //  DISPATCHING RESPONSE UNIT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Syntax collapsing - fragments of prayer stuttering</t>
+          <t>Citizen's device scan fails</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tag_day.fragment.02</t>
+          <t>tag_day.fragment.01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3483,14 +3557,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Life is</t>
+          <t>For Thine is</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Syntax collapsing - fragments of prayer stuttering</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tag_day.fragment.03</t>
+          <t>tag_day.fragment.02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3505,27 +3584,49 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>For Thine is the</t>
+          <t>Life is</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>tag_day.fragment.03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>For Thine is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>tag_day.fragment.04</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>fragment</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>This is the way the world ends
 This is the way the world ends
@@ -3533,42 +3634,15 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>tag_day.fragment.07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Not with a BANG...</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>The final line breaks mid-word</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tag_day.fragment.08</t>
+          <t>tag_day.fragment.07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3578,24 +3652,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>...but a whimper.</t>
+          <t>Not with a BANG...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Muffled behind the closed door</t>
+          <t>The final line breaks mid-word</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tag_day.lockdown</t>
+          <t>tag_day.fragment.08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3605,29 +3679,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
+          <t>...but a whimper.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lockdown alarm after neutralization</t>
+          <t>Muffled behind the closed door</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tag_day.groan</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BYSTANDER</t>
+          <t>tag_day.lockdown</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3637,24 +3706,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Come on... I need to get back to work.</t>
+          <t>MEDICAL BAY PROTOCOL  //  ENFORCEMENT ENABLED  //  PLEASE REMAIN IN POSITION</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bystander reacting to the lockdown delay</t>
+          <t>Lockdown alarm after neutralization</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tag_day.report_blocked</t>
+          <t>tag_day.groan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ASTER</t>
+          <t>BYSTANDER</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3669,29 +3738,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ugh, can't even make an incident report.</t>
+          <t>Come on... I need to get back to work.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aster frustrated - device locked during protocol enforcement</t>
+          <t>Bystander reacting to the lockdown delay</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tag_day.scan_passed</t>
+          <t>tag_day.report_blocked</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STATION 7-B</t>
+          <t>ASTER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3701,37 +3770,69 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
+          <t>Ugh, can't even make an incident report.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aster scans clean</t>
+          <t>Aster frustrated - device locked during protocol enforcement</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>tag_day.scan_passed</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>STATION 7-B</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TAG VERIFICATION: PASSED  //  CLEARANCE NOMINAL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aster scans clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>tag_day.clearance</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Blue light. Clean reading.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Blue clearance - auto-advances into transition</t>
         </is>
@@ -3748,50 +3849,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>junction.dusk</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The light is changing. Dimming.</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Scripted dusk - first nightfall approaching</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>junction.workbench.aster</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>junction.dusk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3801,29 +3902,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sealant applicators. Pressure readers. Manual torque adjusters. No automated systems. Whoever lives here is maintaining this entire section by hand.</t>
+          <t>The light is changing. Dimming.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster examines the workbench</t>
+          <t>Scripted dusk - first nightfall approaching</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>junction.workbench.peris</t>
+          <t>junction.workbench.aster</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3833,29 +3934,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>These are all laid out so carefully. Every tool in its place. Someone really cares about their work.</t>
+          <t>Sealant applicators. Pressure readers. Manual torque adjusters. No automated systems. Whoever lives here is maintaining this entire section by hand.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris examines the workbench</t>
+          <t>Aster examines the workbench</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>junction.monitor.aster</t>
+          <t>junction.workbench.peris</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3865,29 +3966,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barrier integrity readings. Trending downward. Slowly, but consistently. Whoever is logging this has been watching the wall weaken for years.</t>
+          <t>These are all laid out so carefully. Every tool in its place. Someone really cares about their work.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aster reads the monitoring station</t>
+          <t>Peris examines the workbench</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>junction.monitor.peris</t>
+          <t>junction.monitor.aster</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3897,24 +3998,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>All these little gauges. I don't know what they measure but they all look like they're... leaning the wrong way.</t>
+          <t>Barrier integrity readings. Trending downward. Slowly, but consistently. Whoever is logging this has been watching the wall weaken for years.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Peris reads the monitoring station</t>
+          <t>Aster reads the monitoring station</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>junction.food.aster</t>
+          <t>junction.monitor.peris</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3929,24 +4030,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Consuming food you do not own is a breach of protocol.</t>
+          <t>All these little gauges. I don't know what they measure but they all look like they're... leaning the wrong way.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aster at the food cache - compliance over survival</t>
+          <t>Peris reads the monitoring station</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>junction.food.peris</t>
+          <t>junction.food.aster</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3961,29 +4062,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>It's not very nice to take someone else's food!</t>
+          <t>Consuming food you do not own is a breach of protocol.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Peris at the food cache - empathy over survival</t>
+          <t>Aster at the food cache - compliance over survival</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>junction.lookout.aster</t>
+          <t>junction.food.peris</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3993,29 +4094,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Significant wear pattern on the floor here. Someone stands in this exact spot regularly. The window faces the bridge approach.</t>
+          <t>It's not very nice to take someone else's food!</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aster at the lookout spot</t>
+          <t>Peris at the food cache - empathy over survival</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>junction.lookout.peris</t>
+          <t>junction.lookout.aster</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4025,29 +4126,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Someone stands here a lot. Looking out. Waiting for someone.</t>
+          <t>Significant wear pattern on the floor here. Someone stands in this exact spot regularly. The window faces the bridge approach.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Peris at the lookout spot</t>
+          <t>Aster at the lookout spot</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>junction.heater.aster</t>
+          <t>junction.lookout.peris</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4057,29 +4158,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>This heating element is active and positioned at the entrance. Inefficient placement for personal use. It's oriented outward.</t>
+          <t>Someone stands here a lot. Looking out. Waiting for someone.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aster at the heater - data without emotional inference</t>
+          <t>Peris at the lookout spot</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>junction.heater.peris</t>
+          <t>junction.heater.aster</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4089,29 +4190,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>This is warm. It's been running for a while. Someone set it up for visitors.</t>
+          <t>This heating element is active and positioned at the entrance. Inefficient placement for personal use. It's oriented outward.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Peris at the heater - she reads the care</t>
+          <t>Aster at the heater - data without emotional inference</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>junction.markings.aster</t>
+          <t>junction.heater.peris</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4121,29 +4222,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>What annotation format is this? This is definitely not standard!</t>
+          <t>This is warm. It's been running for a while. Someone set it up for visitors.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aster at the wall markings - unrecognized system</t>
+          <t>Peris at the heater - she reads the care</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>junction.markings.peris</t>
+          <t>junction.markings.aster</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4153,24 +4254,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I'm not sure what these markings say, but the handwriting's got a lot of personality.</t>
+          <t>What annotation format is this? This is definitely not standard!</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Peris at the wall markings - she reads the person</t>
+          <t>Aster at the wall markings - unrecognized system</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>junction.game.aster</t>
+          <t>junction.markings.peris</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4185,24 +4286,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Who has time to waste on things like these?</t>
+          <t>I'm not sure what these markings say, but the handwriting's got a lot of personality.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</t>
+          <t>Peris at the wall markings - she reads the person</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>junction.game.peris</t>
+          <t>junction.game.aster</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4217,19 +4318,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</t>
+          <t>Who has time to waste on things like these?</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</t>
+          <t>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>junction.endo.beckon</t>
+          <t>junction.game.peris</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4244,24 +4350,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Someone in the doorway. Beckoning.</t>
+          <t>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Endo gestures them inside - marker appears on shelter</t>
+          <t>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>junction.peris.who</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.beckon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4276,24 +4377,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Who...?</t>
+          <t>Someone in the doorway. Beckoning.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Endo gestures them inside - marker appears on shelter</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>junction.aster.endo_read</t>
+          <t>junction.peris.who</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4303,24 +4409,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Endosomal unit. Non-hostile. His tag reads compliant, but the signal's dead.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Aster scans Endo</t>
+          <t>Who...?</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>junction.endo.drink</t>
+          <t>junction.aster.endo_read</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4330,24 +4436,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>He holds out a container. Points at it, then at them.</t>
+          <t>Endosomal unit. Non-hostile. His tag reads compliant, but the signal's dead.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Endo offers drink - marker on container</t>
+          <t>Aster scans Endo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>junction.peris.stomach</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.drink</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4362,19 +4463,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Can't sleep well on an empty stomach.</t>
+          <t>He holds out a container. Points at it, then at them.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Accepts the drink</t>
+          <t>Endo offers drink - marker on container</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>junction.endo.rest</t>
+          <t>junction.peris.stomach</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4389,24 +4495,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>He moves to the window. Settles against the wall, watching outward.</t>
+          <t>Can't sleep well on an empty stomach.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Endo takes watch - no marker needed</t>
+          <t>Accepts the drink</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>junction.night.eyes</t>
+          <t>junction.endo.rest</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4416,24 +4522,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red. Through the grating. Watching.</t>
+          <t>He moves to the window. Settles against the wall, watching outward.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pairs of eyes outside - the player sees them too</t>
+          <t>Endo takes watch - no marker needed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>junction.dawn</t>
+          <t>junction.night.eyes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4443,19 +4549,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Morning. They're gone.</t>
+          <t>Red. Through the grating. Watching.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The eyes recede with the light</t>
+          <t>Pairs of eyes outside - the player sees them too</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>junction.morning.trail</t>
+          <t>junction.dawn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4470,19 +4576,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A faint wet trail near the shelter door, already drying. It wasn't there last night.</t>
+          <t>Morning. They're gone.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Evidence of the night visitors</t>
+          <t>The eyes recede with the light</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>junction.endo.stands</t>
+          <t>junction.morning.trail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4497,24 +4603,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
+          <t>A faint wet trail near the shelter door, already drying. It wasn't there last night.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Endo gestures: he's coming with</t>
+          <t>Evidence of the night visitors</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>junction.peris.coming</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.stands</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4529,19 +4630,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I think he's coming with us.</t>
+          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Endo gestures: he's coming with</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>junction.aster.ok</t>
+          <t>junction.peris.coming</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4556,14 +4662,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I don't see why not.</t>
+          <t>I think he's coming with us.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>junction.aster.blocked</t>
+          <t>junction.aster.ok</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4573,7 +4679,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4583,29 +4689,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Aster reads the gauntlet</t>
+          <t>I don't see why not.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>junction.peris.ferrolure</t>
+          <t>junction.aster.blocked</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4615,24 +4716,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
+          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Peris recognizes the device</t>
+          <t>Aster reads the gauntlet</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>junction.ferrolure.active</t>
+          <t>junction.peris.ferrolure</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4642,24 +4748,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
+          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>System readout</t>
+          <t>Peris recognizes the device</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>junction.exit_narration</t>
+          <t>junction.ferrolure.active</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4669,19 +4775,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>The facility door seals behind you. The corridor stretches ahead.</t>
+          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leaving the facility</t>
+          <t>System readout</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>junction.endo_appears</t>
+          <t>junction.exit_narration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4696,19 +4802,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
+          <t>The facility door seals behind you. The corridor stretches ahead.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Endo joins - no words</t>
+          <t>Leaving the facility</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>junction.endo.shelters</t>
+          <t>junction.endo_appears</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4723,19 +4829,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
+          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Endo gestures toward shelter - marker appears</t>
+          <t>Endo joins - no words</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>junction.endo.iron_warn</t>
+          <t>junction.endo.shelters</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4750,19 +4856,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
+          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Endo blocks the iron path - marker on safe route</t>
+          <t>Endo gestures toward shelter - marker appears</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>junction.endo.dusk</t>
+          <t>junction.endo.iron_warn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4777,19 +4883,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
+          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Endo notices dusk - urgency without words</t>
+          <t>Endo blocks the iron path - marker on safe route</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>junction.endo.shelter</t>
+          <t>junction.endo.dusk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4804,19 +4910,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>He stops at a door. Opens it. Steps aside.</t>
+          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Endo at the shelter entrance</t>
+          <t>Endo notices dusk - urgency without words</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>junction.night_narration</t>
+          <t>junction.endo.shelter</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4831,19 +4937,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
+          <t>He stops at a door. Opens it. Steps aside.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>First night</t>
+          <t>Endo at the shelter entrance</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>junction.endo.rest</t>
+          <t>junction.night_narration</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4858,37 +4964,64 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>He settles against the wall. Watches the door.</t>
+          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Endo takes watch - same posture as junction</t>
+          <t>First night</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>junction.endo.rest</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>He settles against the wall. Watches the door.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Endo takes watch - same posture as junction</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>junction.dawn</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Day 2. Dawn.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Morning - waits for click</t>
         </is>
@@ -4905,50 +5038,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>channels.narration.enter</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The corridor opens. Water runs along the floor in shallow channels. The air is different here -- cleaner where the water flows, stale where it pools.</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>First view of the Perivascular Channels</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>channels.aster.fluid</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>channels.narration.enter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4958,29 +5091,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fluid dynamics are still active in this section. Flow rate correlates with atmospheric quality. Where it moves, the readings are clean.</t>
+          <t>The corridor opens. Water runs along the floor in shallow channels. The air is different here -- cleaner where the water flows, stale where it pools.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster reads the data</t>
+          <t>First view of the Perivascular Channels</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>channels.peris.sound</t>
+          <t>channels.aster.fluid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4990,19 +5123,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Listen. You can hear it. The moving water sounds different from the still water.</t>
+          <t>Fluid dynamics are still active in this section. Flow rate correlates with atmospheric quality. Where it moves, the readings are clean.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris reads by ear</t>
+          <t>Aster reads the data</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>channels.endo.stop</t>
+          <t>channels.peris.sound</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5017,29 +5155,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>He stops at the edge of a stagnant pool. Shakes his head. Points to the flowing channel beside it.</t>
+          <t>Listen. You can hear it. The moving water sounds different from the still water.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Endo: stagnant = danger</t>
+          <t>Peris reads by ear</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>channels.aster.stagnant</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>channels.endo.stop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5049,29 +5182,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Iron concentration spikes near the stagnant sections. The standing water is concentrating the deposits.</t>
+          <t>He stops at the edge of a stagnant pool. Shakes his head. Points to the flowing channel beside it.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aster confirms</t>
+          <t>Endo: stagnant = danger</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>channels.peris.thick</t>
+          <t>channels.aster.stagnant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5081,19 +5214,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The air is heavier here. Like breathing through cloth.</t>
+          <t>Iron concentration spikes near the stagnant sections. The standing water is concentrating the deposits.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peris feels biofilm</t>
+          <t>Aster confirms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>channels.narration.flora</t>
+          <t>channels.peris.thick</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5108,24 +5246,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Something is growing where the water seeps into the wall. Faint. Not quite alive, not quite dead.</t>
+          <t>The air is heavier here. Like breathing through cloth.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>First wild flora</t>
+          <t>Peris feels biofilm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>channels.peris.touch</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>channels.narration.flora</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5140,29 +5273,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>It responds to me. I just... touched it, and it brightened.</t>
+          <t>Something is growing where the water seeps into the wall. Faint. Not quite alive, not quite dead.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peris discovers tending</t>
+          <t>First wild flora</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>channels.aster.glow</t>
+          <t>channels.peris.touch</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5172,29 +5305,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bioluminescence increased by 40% on contact. Whatever you did, the growth is producing more light now.</t>
+          <t>It responds to me. I just... touched it, and it brightened.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aster measures it</t>
+          <t>Peris discovers tending</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>channels.peris.always</t>
+          <t>channels.aster.glow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5204,19 +5337,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I didn't do anything. Plants just... respond to me. They always have.</t>
+          <t>Bioluminescence increased by 40% on contact. Whatever you did, the growth is producing more light now.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>She doesn't know why</t>
+          <t>Aster measures it</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>channels.narration.branch</t>
+          <t>channels.peris.always</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5231,19 +5369,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The channels branch. One path flows steadily forward. Another leads into silence.</t>
+          <t>I didn't do anything. Plants just... respond to me. They always have.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Route choice</t>
+          <t>She doesn't know why</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>channels.endo.point</t>
+          <t>channels.narration.branch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5258,19 +5396,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>He points toward the flowing channel. Then at the silent branch, and draws a finger across his throat.</t>
+          <t>The channels branch. One path flows steadily forward. Another leads into silence.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>That way is death</t>
+          <t>Route choice</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>channels.narration.body</t>
+          <t>channels.endo.point</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5285,19 +5423,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A figure in the drainage channel. Still. The water flows around them. They stopped moving a long time ago.</t>
+          <t>He points toward the flowing channel. Then at the silent branch, and draws a finger across his throat.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>First lootable corpse</t>
+          <t>That way is death</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>channels.endo.kneel</t>
+          <t>channels.narration.body</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5312,24 +5450,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>He kneels beside the body. A brief pause. Then his hands move -- practiced, efficient. He stands with something in his palm.</t>
+          <t>A figure in the drainage channel. Still. The water flows around them. They stopped moving a long time ago.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Endo demonstrates nutrient absorption</t>
+          <t>First lootable corpse</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>channels.peris.what</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>channels.endo.kneel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5344,29 +5477,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>What did he just...?</t>
+          <t>He kneels beside the body. A brief pause. Then his hands move -- practiced, efficient. He stands with something in his palm.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Peris processing</t>
+          <t>Endo demonstrates nutrient absorption</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>channels.aster.nutrients</t>
+          <t>channels.peris.what</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5376,29 +5509,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Organic nutrient absorption. The biological matter still has caloric value. It is what it is.</t>
+          <t>What did he just...?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clinical framing</t>
+          <t>Peris processing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>channels.peris.people</t>
+          <t>channels.aster.nutrients</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5408,24 +5541,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>These were people.</t>
+          <t>Organic nutrient absorption. The biological matter still has caloric value. It is what it is.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Humane framing</t>
+          <t>Clinical framing</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>channels.aster.hungry</t>
+          <t>channels.peris.people</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5440,19 +5573,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>They were. And we're hungry.</t>
+          <t>These were people.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pragmatism</t>
+          <t>Humane framing</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>channels.narration.shelter</t>
+          <t>channels.aster.hungry</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5467,37 +5605,64 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A sealed alcove beside the main flow. The door responds to proximity. Inside: dry, warm, defensible.</t>
+          <t>They were. And we're hungry.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shelter 2</t>
+          <t>Pragmatism</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>channels.narration.shelter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A sealed alcove beside the main flow. The door responds to proximity. Inside: dry, warm, defensible.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Shelter 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>channels.endo.door</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>He opens the door. Steps aside. The same gesture as the junction.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Endo at shelter</t>
         </is>
@@ -5514,50 +5679,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>stacks.narration.enter</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The drainage channels give way to something industrial. Server racks in rows. Cooling systems humming. The sound of computation.</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Entering the Processing Stacks</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stacks.aster.home</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>stacks.narration.enter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5567,29 +5732,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I know this infrastructure. These are the processing cores. Every data point I've ever analyzed was processed here.</t>
+          <t>The drainage channels give way to something industrial. Server racks in rows. Cooling systems humming. The sound of computation.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster recognizes the hardware</t>
+          <t>Entering the Processing Stacks</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stacks.peris.cold</t>
+          <t>stacks.aster.home</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5599,29 +5764,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>It's cold in here. And loud. How does anyone work in this?</t>
+          <t>I know this infrastructure. These are the processing cores. Every data point I've ever analyzed was processed here.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris in a machine environment</t>
+          <t>Aster recognizes the hardware</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stacks.aster.terminal</t>
+          <t>stacks.peris.cold</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5631,19 +5796,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>There. A maintenance terminal. No friendly interface -- just raw logs.</t>
+          <t>It's cold in here. And loud. How does anyone work in this?</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raw data access</t>
+          <t>Peris in a machine environment</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stacks.aster.cleaned</t>
+          <t>stacks.aster.terminal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5663,19 +5828,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>"The data has been cleaned and normalized to correct for anomalies." The same words. From my desk in the simulation.</t>
+          <t>There. A maintenance terminal. No friendly interface -- just raw logs.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Information trail begins</t>
+          <t>Raw data access</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stacks.aster.here</t>
+          <t>stacks.aster.cleaned</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5685,7 +5850,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5695,24 +5860,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>It happened here. On these servers. Through these conduits. The system that gave me the drink machine is the same one that cleaned my reports.</t>
+          <t>"The data has been cleaned and normalized to correct for anomalies." The same words. From my desk in the simulation.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connecting the dots</t>
+          <t>Information trail begins</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stacks.peris.ok</t>
+          <t>stacks.aster.here</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5727,19 +5892,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Are you OK?</t>
+          <t>It happened here. On these servers. Through these conduits. The system that gave me the drink machine is the same one that cleaned my reports.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Connecting the dots</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stacks.aster.not_sure</t>
+          <t>stacks.peris.ok</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5754,19 +5924,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I'm not sure what I expected to find. But it wasn't this.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Processing the betrayal</t>
+          <t>Are you OK?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stacks.narration.elegant</t>
+          <t>stacks.aster.not_sure</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5781,19 +5951,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>One section is noticeably better than its surroundings. The cable routing is elegant, almost artistic. Someone who cared about this hardware shaped these rows.</t>
+          <t>I'm not sure what I expected to find. But it wasn't this.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Myke retroactive storytelling</t>
+          <t>Processing the betrayal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stacks.narration.closet</t>
+          <t>stacks.narration.elegant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5808,29 +5978,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A small workspace between two racks. A half-finished schematic, crossed out and restarted in the margins. Someone was designing something better and kept stopping.</t>
+          <t>One section is noticeably better than its surroundings. The cable routing is elegant, almost artistic. Someone who cared about this hardware shaped these rows.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Myke was here</t>
+          <t>Myke retroactive storytelling</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stacks.aster.archive</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>stacks.narration.closet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5840,19 +6005,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Older data here. The system keeps its own history in layers. I can read backwards through it.</t>
+          <t>A small workspace between two racks. A half-finished schematic, crossed out and restarted in the margins. Someone was designing something better and kept stopping.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Archive access</t>
+          <t>Myke was here</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stacks.aster.when</t>
+          <t>stacks.aster.archive</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5872,29 +6037,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The normalization started on a specific date. Someone built the protocol. Someone authorized it. The terminal doesn't say who, but it shows when.</t>
+          <t>Older data here. The system keeps its own history in layers. I can read backwards through it.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The trail has a beginning</t>
+          <t>Archive access</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stacks.peris.meaning</t>
+          <t>stacks.aster.when</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5904,37 +6069,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>What does that mean for us?</t>
+          <t>The normalization started on a specific date. Someone built the protocol. Someone authorized it. The terminal doesn't say who, but it shows when.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The trail has a beginning</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>stacks.peris.meaning</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>What does that mean for us?</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>stacks.aster.means</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Aster</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>It means the data isn't broken. Someone is making it wrong. On purpose.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Not failure - policy</t>
         </is>
@@ -5951,50 +6148,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>rings.narration.enter</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The corridors change. Clean. Lit. Warm. People walk past on their own routines. Simulation bays glow through windows.</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Entering the Residential Rings</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rings.aster.signal</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>rings.narration.enter</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6004,29 +6201,29 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>System signals everywhere. Processing stations, transit routing, the full network. This is civilization.</t>
+          <t>The corridors change. Clean. Lit. Warm. People walk past on their own routines. Simulation bays glow through windows.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aster reads the infrastructure</t>
+          <t>Entering the Residential Rings</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rings.peris.remember</t>
+          <t>rings.aster.signal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6036,19 +6233,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I know this place. My clients lived here. The inner ones.</t>
+          <t>System signals everywhere. Processing stations, transit routing, the full network. This is civilization.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peris recognizes territory</t>
+          <t>Aster reads the infrastructure</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rings.peris.hello</t>
+          <t>rings.peris.remember</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6068,19 +6265,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hello? It... it's me. Peris. From the feed.</t>
+          <t>I know this place. My clients lived here. The inner ones.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tries to connect</t>
+          <t>Peris recognizes territory</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rings.narration.client</t>
+          <t>rings.peris.hello</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6095,24 +6297,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The client looks confused. Recognizes the voice but not the face. They hurry away.</t>
+          <t>Hello? It... it's me. Peris. From the feed.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The feed was a wall</t>
+          <t>Tries to connect</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rings.peris.wall</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>rings.narration.client</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6127,19 +6324,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The feed was supposed to connect us. It was a wall the whole time.</t>
+          <t>The client looks confused. Recognizes the voice but not the face. They hurry away.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peris realizes</t>
+          <t>The feed was a wall</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rings.narration.empty</t>
+          <t>rings.peris.wall</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6154,29 +6356,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Some apartments are empty. The system lists the occupants as "reassigned." Their belongings are still on the shelves.</t>
+          <t>The feed was supposed to connect us. It was a wall the whole time.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Disappearance</t>
+          <t>Peris realizes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rings.aster.tags</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>rings.narration.empty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6186,24 +6383,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Our tags are still flagged here. We can see all of this, but we can't participate.</t>
+          <t>Some apartments are empty. The system lists the occupants as "reassigned." Their belongings are still on the shelves.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghosts</t>
+          <t>Disappearance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rings.endo.discomfort</t>
+          <t>rings.aster.tags</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6213,19 +6415,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>He's checking behind them more often. His movements are less fluid. He keeps touching the walls.</t>
+          <t>Our tags are still flagged here. We can see all of this, but we can't participate.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Endo far from his wall</t>
+          <t>Ghosts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rings.endo.stops</t>
+          <t>rings.endo.discomfort</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6240,24 +6442,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>He stops. Looks back. Looks forward. Looks at them. Then turns around.</t>
+          <t>He's checking behind them more often. His movements are less fluid. He keeps touching the walls.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Endo chooses the wall</t>
+          <t>Endo far from his wall</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rings.peris.endo</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>rings.endo.stops</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6272,14 +6469,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Endo?</t>
+          <t>He stops. Looks back. Looks forward. Looks at them. Then turns around.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Endo chooses the wall</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rings.narration.leaving</t>
+          <t>rings.peris.endo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6294,24 +6501,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>He doesn't explain. He's already walking back. His section of the wall needs him.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Endothelial cells don't travel</t>
+          <t>Endo?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rings.peris.understands</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>rings.narration.leaving</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6326,24 +6523,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I understand. Some people can only function in their own space.</t>
+          <t>He doesn't explain. He's already walking back. His section of the wall needs him.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Social worker reading</t>
+          <t>Endothelial cells don't travel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rings.aster.just_us</t>
+          <t>rings.peris.understands</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6358,37 +6555,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>So it's just us now.</t>
+          <t>I understand. Some people can only function in their own space.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Social worker reading</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>rings.aster.just_us</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>So it's just us now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>rings.peris.visiting</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Peris</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>It's been just us since the elevator. Endo was visiting.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Reframe: Endo was the guest</t>
         </is>
@@ -6405,50 +6634,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lockout.narration.clean</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>style</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>The corridors get cleaner. The clicking fades. The air smells filtered. Infrastructure lights improve.</t>
+          <t>text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Approaching the boundary</t>
+          <t>context</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lockout.aster.signals</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>lockout.narration.clean</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6458,19 +6687,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>System signals are strong here. Processing stations, transit routing. We're close.</t>
+          <t>The corridors get cleaner. The clicking fades. The air smells filtered. Infrastructure lights improve.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Proximity to civilization</t>
+          <t>Approaching the boundary</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lockout.aster.panel</t>
+          <t>lockout.aster.signals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6490,24 +6719,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Access panel. Standard interface. Let me just...</t>
+          <t>System signals are strong here. Processing stations, transit routing. We're close.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aster tries to interface</t>
+          <t>Proximity to civilization</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lockout.system.rejected</t>
+          <t>lockout.aster.panel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6522,29 +6751,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NON-COMPLIANT: WELLNESS PROTOCOL DEVIATION. ACCESS REVOKED.</t>
+          <t>Access panel. Standard interface. Let me just...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rejection</t>
+          <t>Aster tries to interface</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lockout.aster.again</t>
+          <t>lockout.system.rejected</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6554,29 +6783,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No. Let me try again.</t>
+          <t>NON-COMPLIANT: WELLNESS PROTOCOL DEVIATION. ACCESS REVOKED.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Denial</t>
+          <t>Rejection</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lockout.system.rejected2</t>
+          <t>lockout.aster.again</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6586,29 +6815,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ACCESS REVOKED. REPORT TO NEAREST PROCESSING STATION.</t>
+          <t>No. Let me try again.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Same result</t>
+          <t>Denial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lockout.aster.hack</t>
+          <t>lockout.system.rejected2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6618,29 +6847,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I can hack it. I hacked the elevator. I can hack this.</t>
+          <t>ACCESS REVOKED. REPORT TO NEAREST PROCESSING STATION.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brute force attempt</t>
+          <t>Same result</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lockout.system.blocked</t>
+          <t>lockout.aster.hack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6650,24 +6879,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED ACCESS ATTEMPT LOGGED. RESPONSE UNIT DISPATCHED.</t>
+          <t>I can hack it. I hacked the elevator. I can hack this.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Triggers enforcers</t>
+          <t>Brute force attempt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lockout.narration.footsteps</t>
+          <t>lockout.system.blocked</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6677,24 +6911,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coordinated footsteps. The scan-sweep sound. The calm efficiency of units following protocol.</t>
+          <t>UNAUTHORIZED ACCESS ATTEMPT LOGGED. RESPONSE UNIT DISPATCHED.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Naturalizers converging</t>
+          <t>Triggers enforcers</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lockout.peris.run</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>lockout.narration.footsteps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6709,14 +6938,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>We need to go. Now.</t>
+          <t>Coordinated footsteps. The scan-sweep sound. The calm efficiency of units following protocol.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Naturalizers converging</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lockout.narration.chase</t>
+          <t>lockout.peris.run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6731,19 +6970,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>They run. The Naturalizers don't. They walk with purpose. The gentle hands from Tag Day are reaching for them.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>The chase</t>
+          <t>We need to go. Now.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lockout.narration.boundary</t>
+          <t>lockout.narration.chase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6758,24 +6992,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The Naturalizers stop at the boundary where the system's infrastructure ends. They stand. They scan. They wait.</t>
+          <t>They run. The Naturalizers don't. They walk with purpose. The gentle hands from Tag Day are reaching for them.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The system does not extend here</t>
+          <t>The chase</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lockout.aster.not_in</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>lockout.narration.boundary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6790,24 +7019,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>It's not letting me back in.</t>
+          <t>The Naturalizers stop at the boundary where the system's infrastructure ends. They stand. They scan. They wait.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The real lockout</t>
+          <t>The system does not extend here</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lockout.peris.back_to</t>
+          <t>lockout.aster.not_in</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6822,37 +7051,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>...Back in to what?</t>
+          <t>It's not letting me back in.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not rhetorical</t>
+          <t>The real lockout</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>lockout.peris.back_to</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>...Back in to what?</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not rhetorical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>lockout.narration.forward</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>The Naturalizers watch from the boundary. The clicking of Chelators resumes behind them. There is no going back.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Exile is permanent</t>
         </is>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -3849,7 +3849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3887,7 +3887,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>junction.dusk</t>
+          <t>junction.peris.tend_plant</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3902,29 +3907,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The light is changing. Dimming.</t>
+          <t>Something's still alive in here. Just barely.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scripted dusk - first nightfall approaching</t>
+          <t>Peris tends the dormant plant, triggering dusk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>junction.workbench.aster</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Aster</t>
+          <t>junction.dusk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3934,29 +3934,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sealant applicators. Pressure readers. Manual torque adjusters. No automated systems. Whoever lives here is maintaining this entire section by hand.</t>
+          <t>The light is changing. Dimming.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aster examines the workbench</t>
+          <t>Scripted dusk - first nightfall approaching</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>junction.workbench.peris</t>
+          <t>junction.workbench.aster</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3966,29 +3966,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>These are all laid out so carefully. Every tool in its place. Someone really cares about their work.</t>
+          <t>Sealant applicators. Pressure readers. Manual torque adjusters. No automated systems. Whoever lives here is maintaining this entire section by hand.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Peris examines the workbench</t>
+          <t>Aster examines the workbench</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>junction.monitor.aster</t>
+          <t>junction.workbench.peris</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3998,29 +3998,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barrier integrity readings. Trending downward. Slowly, but consistently. Whoever is logging this has been watching the wall weaken for years.</t>
+          <t>These are all laid out so carefully. Every tool in its place. Someone really cares about their work.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aster reads the monitoring station</t>
+          <t>Peris examines the workbench</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>junction.monitor.peris</t>
+          <t>junction.monitor.aster</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4030,24 +4030,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>All these little gauges. I don't know what they measure but they all look like they're... leaning the wrong way.</t>
+          <t>Barrier integrity readings. Trending downward. Slowly, but consistently. Whoever is logging this has been watching the wall weaken for years.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Peris reads the monitoring station</t>
+          <t>Aster reads the monitoring station</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>junction.food.aster</t>
+          <t>junction.monitor.peris</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4062,24 +4062,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consuming food you do not own is a breach of protocol.</t>
+          <t>All these little gauges. I don't know what they measure but they all look like they're... leaning the wrong way.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aster at the food cache - compliance over survival</t>
+          <t>Peris reads the monitoring station</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>junction.food.peris</t>
+          <t>junction.food.aster</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4094,29 +4094,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>It's not very nice to take someone else's food!</t>
+          <t>Consuming food you do not own is a breach of protocol.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Peris at the food cache - empathy over survival</t>
+          <t>Aster at the food cache and makes a Chrono Trigger reference</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>junction.lookout.aster</t>
+          <t>junction.food.peris</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4126,29 +4126,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Significant wear pattern on the floor here. Someone stands in this exact spot regularly. The window faces the bridge approach.</t>
+          <t>It's not very nice to take someone else's food!</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aster at the lookout spot</t>
+          <t>I'm still mad I got all guilty during the Chrono Trigger trial scene for trying to experience the game. How Heidiggerian of me lmao</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>junction.lookout.peris</t>
+          <t>junction.lookout.aster</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4158,29 +4158,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Someone stands here a lot. Looking out. Waiting for someone.</t>
+          <t>Significant wear pattern on the floor here. Someone stands in this exact spot regularly. The window faces the bridge approach.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Peris at the lookout spot</t>
+          <t>Aster at the lookout spot</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>junction.heater.aster</t>
+          <t>junction.lookout.peris</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4190,29 +4190,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>This heating element is active and positioned at the entrance. Inefficient placement for personal use. It's oriented outward.</t>
+          <t>Someone stands here a lot. Looking out. Waiting for someone.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aster at the heater - data without emotional inference</t>
+          <t>Peris at the lookout spot</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>junction.heater.peris</t>
+          <t>junction.heater.aster</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4222,29 +4222,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>This is warm. It's been running for a while. Someone set it up for visitors.</t>
+          <t>This heating element is active and positioned at the entrance. Inefficient placement for personal use. It's oriented outward.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Peris at the heater - she reads the care</t>
+          <t>My electric bill is rolling in its grave</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>junction.markings.aster</t>
+          <t>junction.heater.peris</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4254,29 +4254,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>What annotation format is this? This is definitely not standard!</t>
+          <t>This is warm. It's been running for a while. Someone set it up for visitors.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aster at the wall markings - unrecognized system</t>
+          <t>Peris at the heater - she reads the care</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>junction.markings.peris</t>
+          <t>junction.markings.aster</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4286,24 +4286,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I'm not sure what these markings say, but the handwriting's got a lot of personality.</t>
+          <t>What annotation format is this? This is definitely not standard!</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Peris at the wall markings - she reads the person</t>
+          <t>Aster at the wall markings - unrecognized system</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>junction.game.aster</t>
+          <t>junction.markings.peris</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4318,24 +4318,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Who has time to waste on things like these?</t>
+          <t>I'm not sure what these markings say, but the handwriting's got a lot of personality.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</t>
+          <t>Peris at the wall markings - she reads the person</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>junction.game.peris</t>
+          <t>junction.game.aster</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4350,19 +4350,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</t>
+          <t>Who has time to waste on things like these?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</t>
+          <t>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>junction.endo.beckon</t>
+          <t>junction.game.peris</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4377,24 +4382,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Someone in the doorway. Beckoning.</t>
+          <t>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Endo gestures them inside - marker appears on shelter</t>
+          <t>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>junction.peris.who</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.beckon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4409,24 +4409,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Who...?</t>
+          <t>Someone in the doorway. Beckoning.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Endo gestures them inside - marker appears on shelter</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>junction.aster.endo_read</t>
+          <t>junction.peris.who</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4436,24 +4441,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Endosomal unit. Non-hostile. His tag reads compliant, but the signal's dead.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Aster scans Endo</t>
+          <t>Who...?</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>junction.endo.drink</t>
+          <t>junction.aster.endo_read</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4463,24 +4468,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>He holds out a container. Points at it, then at them.</t>
+          <t>Endosomal unit. Non-hostile. His tag reads compliant, but the signal's dead.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Endo offers drink - marker on container</t>
+          <t>Aster scans Endo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>junction.peris.stomach</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.drink</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4495,19 +4495,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Can't sleep well on an empty stomach.</t>
+          <t>He holds out a container. Points at it, then at them.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Accepts the drink</t>
+          <t>Endo offers drink - marker on container</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>junction.endo.rest</t>
+          <t>junction.peris.stomach</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4522,24 +4527,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>He moves to the window. Settles against the wall, watching outward.</t>
+          <t>Can't sleep well on an empty stomach.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Endo takes watch - no marker needed</t>
+          <t>Accepts the drink</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>junction.night.eyes</t>
+          <t>junction.endo.rest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>poem</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4549,24 +4554,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red. Through the grating. Watching.</t>
+          <t>He moves to the window. Settles against the wall, watching outward.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pairs of eyes outside - the player sees them too</t>
+          <t>Endo takes watch - no marker needed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>junction.dawn</t>
+          <t>junction.night.eyes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>poem</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4576,19 +4581,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Morning. They're gone.</t>
+          <t>Red. Through the grating. Watching.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>The eyes recede with the light</t>
+          <t>Pairs of eyes outside - the player sees them too</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>junction.morning.trail</t>
+          <t>junction.dawn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4603,19 +4608,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A faint wet trail near the shelter door, already drying. It wasn't there last night.</t>
+          <t>Morning. They're gone.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Evidence of the night visitors</t>
+          <t>The eyes recede with the light</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>junction.endo.stands</t>
+          <t>junction.morning.trail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4630,24 +4635,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
+          <t>A faint wet trail near the shelter door, already drying. It wasn't there last night.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Endo gestures: he's coming with</t>
+          <t>Evidence of the night visitors</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>junction.peris.coming</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>junction.endo.stands</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4662,19 +4662,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I think he's coming with us.</t>
+          <t>He stands. Looks at the corridor ahead, then at them. Steps toward the door.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Endo gestures: he's coming with</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>junction.aster.ok</t>
+          <t>junction.peris.coming</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aster</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4689,14 +4694,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I don't see why not.</t>
+          <t>I think he's coming with us.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>junction.aster.blocked</t>
+          <t>junction.aster.ok</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4706,7 +4711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4716,29 +4721,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Aster reads the gauntlet</t>
+          <t>I don't see why not.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>junction.peris.ferrolure</t>
+          <t>junction.aster.blocked</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4748,24 +4748,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
+          <t>Dense cluster ahead. Five, maybe six. Too many to push through.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Peris recognizes the device</t>
+          <t>Aster reads the gauntlet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>junction.ferrolure.active</t>
+          <t>junction.peris.ferrolure</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4775,24 +4780,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
+          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>System readout</t>
+          <t>Peris recognizes the device</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>junction.exit_narration</t>
+          <t>junction.ferrolure.active</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4802,19 +4807,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The facility door seals behind you. The corridor stretches ahead.</t>
+          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leaving the facility</t>
+          <t>System readout</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>junction.endo_appears</t>
+          <t>junction.exit_narration</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4829,19 +4834,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
+          <t>The facility door seals behind you. The corridor stretches ahead.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Endo joins - no words</t>
+          <t>Leaving the facility</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>junction.endo.shelters</t>
+          <t>junction.endo_appears</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4856,19 +4861,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
+          <t>Someone is waiting at the exit. Quiet. Watchful. He falls into step beside you.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Endo gestures toward shelter - marker appears</t>
+          <t>Endo joins - no words</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>junction.endo.iron_warn</t>
+          <t>junction.endo.shelters</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4883,19 +4888,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
+          <t>He points ahead. Then at a marker on the wall -- a shelter symbol.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Endo blocks the iron path - marker on safe route</t>
+          <t>Endo gestures toward shelter - marker appears</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>junction.endo.dusk</t>
+          <t>junction.endo.iron_warn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4910,19 +4915,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
+          <t>He stops. Holds out an arm. Shakes his head slowly.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Endo notices dusk - urgency without words</t>
+          <t>Endo blocks the iron path - marker on safe route</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>junction.endo.shelter</t>
+          <t>junction.endo.dusk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4937,19 +4942,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>He stops at a door. Opens it. Steps aside.</t>
+          <t>He taps the wall. Points at the dimming light. Walks faster.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Endo at the shelter entrance</t>
+          <t>Endo notices dusk - urgency without words</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>junction.night_narration</t>
+          <t>junction.endo.shelter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4964,19 +4969,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
+          <t>He stops at a door. Opens it. Steps aside.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>First night</t>
+          <t>Endo at the shelter entrance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>junction.endo.rest</t>
+          <t>junction.night_narration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4991,37 +4996,64 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>He settles against the wall. Watches the door.</t>
+          <t>Night. The barrier is thinner here. You can hear things moving outside.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Endo takes watch - same posture as junction</t>
+          <t>First night</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>junction.endo.rest</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>He settles against the wall. Watches the door.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Endo takes watch - same posture as junction</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>junction.dawn</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Day 2. Dawn.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Morning - waits for click</t>
         </is>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -1483,7 +1483,7 @@
         <v>false</v>
       </c>
       <c r="E18" t="str">
-        <v>My device. It's back. There's a maintenance panel behind the doors.</v>
+        <v>Looks like my perks are coming in handy. There's a maintenance panel behind the doors!</v>
       </c>
       <c r="F18" t="str">
         <v>Aster's data overlay reveals the panel</v>
@@ -1523,10 +1523,10 @@
         <v>false</v>
       </c>
       <c r="E20" t="str">
-        <v>No no no. My device. I can pulse it, fry their circuits.</v>
+        <v>Hey, want to see a perk I haven't tried yet?</v>
       </c>
       <c r="F20" t="str">
-        <v>Aster panicking but finding a solution</v>
+        <v>Aster about to use EMP</v>
       </c>
     </row>
     <row r="21">
@@ -1800,7 +1800,7 @@
         <v>They might have called me a beast, but I'm not this type of animal...</v>
       </c>
       <c r="F34" t="str">
-        <v>Looking up at the collapsed bridge - no way back up</v>
+        <v xml:space="preserve">This is totally a reference to Reanimal </v>
       </c>
     </row>
     <row r="35">
@@ -1819,6 +1819,9 @@
       <c r="E35" t="str">
         <v>We've got the combined strength of two children. It wouldn't be physically possible to climb this...</v>
       </c>
+      <c r="F35" t="str">
+        <v>I loved Reanimal but those kids were built different</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1834,10 +1837,10 @@
         <v>false</v>
       </c>
       <c r="E36" t="str">
-        <v>There's something over there. Another way forward.</v>
+        <v>Huh, looks like there's [TBD] though...</v>
       </c>
       <c r="F36" t="str">
-        <v>Finds the alternative path (TBD)</v>
+        <v>Something is found in the cracks (TBD)</v>
       </c>
     </row>
     <row r="37">
@@ -2221,7 +2224,7 @@
 For Thine is the Kingdom</v>
       </c>
       <c r="F18" t="str">
-        <v>Final refrain before collapse</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -2241,7 +2244,7 @@
         <v>There's still time.</v>
       </c>
       <c r="F19" t="str">
-        <v>NK-01 down to bare assertion</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -2261,7 +2264,7 @@
         <v>Is there? You're what, twenty-three? Twenty-four?</v>
       </c>
       <c r="F20" t="str">
-        <v>NK-02 names the number - casual and terminal</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2296,7 +2299,7 @@
 Prickly pear prickly pear</v>
       </c>
       <c r="F22" t="str">
-        <v>Citizen murmuring in queue - nursery rhyme draws attention</v>
+        <v>Time for T.S. Elliot, thanks public domain</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
@@ -2314,7 +2317,7 @@
 At five o'clock in the morning.</v>
       </c>
       <c r="F23" t="str">
-        <v>Citizen continues in queue before scan</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -2351,7 +2354,7 @@
         <v>For Thine is</v>
       </c>
       <c r="F25" t="str">
-        <v>Syntax collapsing - fragments of prayer stuttering</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2608,7 +2611,7 @@
         <v>false</v>
       </c>
       <c r="E4" t="str">
-        <v>Sealant applicators. Pressure readers. Manual torque adjusters. No automated systems. Whoever lives here is maintaining this entire section by hand.</v>
+        <v>Sealant applicators. Pressure readers. Manual torque adjusters. Looks like someone missed the automation assisance memo...</v>
       </c>
       <c r="F4" t="str">
         <v>Aster examines the workbench</v>
@@ -2628,10 +2631,10 @@
         <v>false</v>
       </c>
       <c r="E5" t="str">
-        <v>These are all laid out so carefully. Every tool in its place. Someone really cares about their work.</v>
+        <v>I remember a client saying they keep their home neat because it reflects the values they'd want to show in the outside world. I wonder if someone's doing the same?</v>
       </c>
       <c r="F5" t="str">
-        <v>Peris examines the workbench</v>
+        <v>Peris examines workbench (Thanks Arendt for the discussion of private vs. public and the invasion of the social in The Human Condition)</v>
       </c>
     </row>
     <row r="6">
@@ -2648,7 +2651,7 @@
         <v>false</v>
       </c>
       <c r="E6" t="str">
-        <v>Barrier integrity readings. Trending downward. Slowly, but consistently. Whoever is logging this has been watching the wall weaken for years.</v>
+        <v>Why are these barrier integrity readings still going down? I thought the other team was assigned to this!</v>
       </c>
       <c r="F6" t="str">
         <v>Aster reads the monitoring station</v>
@@ -2668,7 +2671,7 @@
         <v>false</v>
       </c>
       <c r="E7" t="str">
-        <v>All these little gauges. I don't know what they measure but they all look like they're... leaning the wrong way.</v>
+        <v>I bet Aster would know how to read these! All I can read is how antsy he seems...</v>
       </c>
       <c r="F7" t="str">
         <v>Peris reads the monitoring station</v>
@@ -2688,7 +2691,7 @@
         <v>false</v>
       </c>
       <c r="E8" t="str">
-        <v>Consuming food you do not own is a breach of protocol.</v>
+        <v>Consuming food you do not own is a breach of protocol. Would look awful in a trial.</v>
       </c>
       <c r="F8" t="str">
         <v>Aster at the food cache and makes a Chrono Trigger reference</v>
@@ -2728,7 +2731,7 @@
         <v>false</v>
       </c>
       <c r="E10" t="str">
-        <v>Significant wear pattern on the floor here. Someone stands in this exact spot regularly. The window faces the bridge approach.</v>
+        <v>Ugh, look at the mess outside. At least whoever lives here seems to be competent...</v>
       </c>
       <c r="F10" t="str">
         <v>Aster at the lookout spot</v>
@@ -2748,7 +2751,7 @@
         <v>false</v>
       </c>
       <c r="E11" t="str">
-        <v>Someone stands here a lot. Looking out. Waiting for someone.</v>
+        <v>Look at the view! It's like what I've seen through client portals!</v>
       </c>
       <c r="F11" t="str">
         <v>Peris at the lookout spot</v>
@@ -2768,7 +2771,7 @@
         <v>false</v>
       </c>
       <c r="E12" t="str">
-        <v>This heating element is active and positioned at the entrance. Inefficient placement for personal use. It's oriented outward.</v>
+        <v>A heater right next to the entrance? The heat's going to leak right out!</v>
       </c>
       <c r="F12" t="str">
         <v>My electric bill is rolling in its grave</v>
@@ -2788,7 +2791,7 @@
         <v>false</v>
       </c>
       <c r="E13" t="str">
-        <v>This is warm. It's been running for a while. Someone set it up for visitors.</v>
+        <v>Looks like someone wanted to give a warm welcome!</v>
       </c>
       <c r="F13" t="str">
         <v>Peris at the heater - she reads the care</v>
@@ -2848,7 +2851,7 @@
         <v>false</v>
       </c>
       <c r="E16" t="str">
-        <v>Who has time to waste on things like these?</v>
+        <v>*Lot Clot*. Who has time to waste on things like these? Glad they invented portals and working *in simulo*...</v>
       </c>
       <c r="F16" t="str">
         <v>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</v>
@@ -2868,7 +2871,7 @@
         <v>false</v>
       </c>
       <c r="E17" t="str">
-        <v>Oh, it's a little puzzle. Someone made this by hand. Look how smooth the edges are from use.</v>
+        <v>*Lot Clot*. Ooh, a traffic jam? Vehicles? How vintage!</v>
       </c>
       <c r="F17" t="str">
         <v>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</v>
@@ -2885,7 +2888,7 @@
         <v>false</v>
       </c>
       <c r="E18" t="str">
-        <v>Someone in the doorway. Beckoning.</v>
+        <v>Hey, someone's here!</v>
       </c>
       <c r="F18" t="str">
         <v>Endo gestures them inside - marker appears on shelter</v>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -2774,7 +2774,7 @@
         <v>A heater right next to the entrance? The heat's going to leak right out!</v>
       </c>
       <c r="F12" t="str">
-        <v>My electric bill is rolling in its grave</v>
+        <v>Aster at the heater (My electric bill is rolling in its grave)</v>
       </c>
     </row>
     <row r="13">
@@ -2794,7 +2794,7 @@
         <v>Looks like someone wanted to give a warm welcome!</v>
       </c>
       <c r="F13" t="str">
-        <v>Peris at the heater - she reads the care</v>
+        <v>Peris at the heater</v>
       </c>
     </row>
     <row r="14">
@@ -2814,7 +2814,7 @@
         <v>What annotation format is this? This is definitely not standard!</v>
       </c>
       <c r="F14" t="str">
-        <v>Aster at the wall markings - unrecognized system</v>
+        <v>Aster at the wall markings</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>I'm not sure what these markings say, but the handwriting's got a lot of personality.</v>
       </c>
       <c r="F15" t="str">
-        <v>Peris at the wall markings - she reads the person</v>
+        <v>Peris at the wall markings</v>
       </c>
     </row>
     <row r="16">
@@ -2854,7 +2854,7 @@
         <v>*Lot Clot*. Who has time to waste on things like these? Glad they invented portals and working *in simulo*...</v>
       </c>
       <c r="F16" t="str">
-        <v>Aster can't fathom leisure - "Lot Clot" scratched into the base plate</v>
+        <v>Aster Peris reacts to "Lot Clot"</v>
       </c>
     </row>
     <row r="17">
@@ -2874,7 +2874,7 @@
         <v>*Lot Clot*. Ooh, a traffic jam? Vehicles? How vintage!</v>
       </c>
       <c r="F17" t="str">
-        <v>Peris sees the care and the years of play - sliding block puzzle about clearing blockages</v>
+        <v>Peris reacts to "Lot Clot"</v>
       </c>
     </row>
     <row r="18">
@@ -3362,7 +3362,7 @@
         <v>Fluid dynamics are still active in this section. Flow rate correlates with atmospheric quality. Where it moves, the readings are clean.</v>
       </c>
       <c r="F3" t="str">
-        <v>Aster reads the data</v>
+        <v>Aster analyzes fluid</v>
       </c>
     </row>
     <row r="4">
@@ -3382,7 +3382,7 @@
         <v>Listen. You can hear it. The moving water sounds different from the still water.</v>
       </c>
       <c r="F4" t="str">
-        <v>Peris reads by ear</v>
+        <v>Peris hears the fluid</v>
       </c>
     </row>
     <row r="5">
@@ -3641,7 +3641,7 @@
         <v>false</v>
       </c>
       <c r="E18" t="str">
-        <v>These were people.</v>
+        <v>These were people...</v>
       </c>
       <c r="F18" t="str">
         <v>Humane framing</v>
@@ -3661,7 +3661,7 @@
         <v>false</v>
       </c>
       <c r="E19" t="str">
-        <v>They were. And we're hungry.</v>
+        <v>And these will be us if we don't eat! It's a downgrade for me too, you know...</v>
       </c>
       <c r="F19" t="str">
         <v>Pragmatism</v>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -12,6 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacks" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="residential-rings" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lockout" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mother-flure" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dead-flure" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endo-wall" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="post-flure" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marco-drag" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="myke-stacks" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nustle" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -453,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +825,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aster_sim.device.tag_verify</t>
+          <t>aster_sim.ron.lighting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEVICE</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -838,24 +845,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TAG VERIFICATION // CHECKPOINT 7-B // REPORT WITHIN 15 MINUTES</t>
+          <t>Geez, Aster, it looks like an evil lair in here. You ever think about turning the lights up?</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Device notification</t>
+          <t>Ron ribs Aster about his warm/dim workspace lighting while walking out; performative concern, friendly and incurious</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aster_sim.ron.tag_notify</t>
+          <t>aster_sim.aster.lighting</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Aster</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -870,39 +877,7284 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ah, sorry to have to pull you out. You're on a roll!</t>
+          <t>The default's like working on the surface of the sun. I cannot deal with it.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ron reacts to the device notification</t>
+          <t>Aster answers matter-of-factly; Ron is already leaving and does not meaningfully take it in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>aster_sim.device.tag_verify</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEVICE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TAG VERIFICATION // CHECKPOINT 7-B // REPORT WITHIN 15 MINUTES</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Device notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>aster_sim.ron.tag_notify</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ah, sorry to have to pull you out. You're on a roll!</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ron reacts to the device notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>aster_sim.tag_routine</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Man, they should really automate these checks sometime...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aster reacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.glass_bead.look</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aster approaches the glass bead game. He picks up a single bead from the side tray, rolls it briefly between his thumb and forefinger, and flicks it toward the levitation field. The bead catches the laser net, starts spinning as the lasers pick it up and weave it into the pattern. The configuration reconfigures briefly around the new addition, then settles. Aster watches it settle.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Approach beat; engagement is casual and physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.glass_bead.line</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Some people take this game seriously. I just like how the beads spin.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Small, private, un-institutional — the one tactile pleasure he hasn't routed through metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.painting_1.look</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aster stops in front of the first painting. His expression lightens with appreciation.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Approach beat for Macabre Teal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.painting_1.line</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>This one's my favorite. Macabre Teal. Spoke to me somehow. Floor price tripled after the burn.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Aesthetic response validated through market movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.painting_2.look</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aster moves to the second painting.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Approach beat for Hunter and Ash</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.painting_2.line</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>And this one's Hunter and Ash. Exclusive collection. They digitized old diagrams as art pieces, then made the originals into a papier-mache sculpture. Up twelve times from auction. I got mine before the burn.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Institutional-investor voice; destruction cycle framed as appreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.awards.look</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aster approaches the awards shelf. He touches the largest, centerpiece plaque lightly with his fingertips.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Approach beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.awards.line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Number one in adjusted citation score median, physical transfer data analysis. Three quarters running. Probably going to win it again, if nothing weird happens to the baseline.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Genuine pride in a category narrowed to produce exactly one #1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.awards.journalism_look</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aster moves along the shelf to another award, a medallion paired with a small framed article-excerpt. He touches the medallion in the same casual way he touched the first plaque.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Same gesture, same frame — no distinction from the preceding award</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.awards.journalism_line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ah, my Safety Communication Prize. Someone had to write about the Junction Barrier Fault incident. Hopefully the loved ones of the seven dead and sixty-two injured can find some justice. Committee said it made the technical content accessible. Good to know some of the work reaches people.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pride in narrating the post-mortem of a failure his ignored prediction would have prevented</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.bookshelf.look</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aster glances at the J-store shelf. His posture straightens slightly — the small physical tell of someone approaching an object they are proud of.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Approach beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.bookshelf.line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>My collection of J-stores. I've been featured in Journal of Adjusted Transfer Analysis, Annals of Baseline Normalization Methodology, Physical Infrastructure Quantification: Meta-Review. Hope my writings help make someone else's office look smarter too!</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sincere institutional pride; 'help make someone else's office look smarter' delivered without irony</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.bookshelf.articles_pull</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aster pulls down one of the J-stores from the shelf. Its interface activates in his hand, displaying the volume's table of contents. He scrolls to his own contributions, which are bookmarked. The player can see several paper titles on the interface.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Optional second-layer approach beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>aster.sim_expand.bookshelf.articles_line</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Most of my work is on barrier fault prediction. "A prospective model for predicting barrier faults" in this one. "Modeling for fault prediction: a potentially useful system for barrier improvement" in the next volume. "The critical importance of barrier integrity for safety" here. A few others building out the framework. I keep refining the approach.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Publication-unit rephrasing of the same underlying prediction work</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.pre.aster.route</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This corridor's our route around, right? Through to the core facility side?</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Light, procedural route check as the party approaches the chamber</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.narration</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The corridor opens. The floor is patterned with rectangular strips of organic root, threaded along channels. At the far end, something rooted to the floor and larger than any flora the party has seen. Across the chamber wall, a mechanical socket missing its gear. The gear itself rests in the middle distance, in a lane the party cannot reach.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>First view of the chamber</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.peris.wow</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wow! How beautiful! I've never seen anything like this!</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pure wonder; unmediated flora at scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.aster.strange</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Strange. Chemical signals point to flure secretions.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Awe processed as anomaly</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.endo.orient</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Endo's posture shifts. He's looking at the floor patterns, then the gear, then the lanes between. Something has clicked for him in a way it hasn't for the others.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Endo's silent recognition (visible body language, no dialogue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.peris.roots</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>What a massive tangle of roots!</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wonder at the physical scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mother_flure.entry.aster.composition</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>The composition's uneven. Some sections are structurally dense but barely vascularized. That's not a growth pattern you'd see in a healthy organism.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Seed for the portal-stress lore thread</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mother_flure.first.peris.trembling</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>I feel my feet trembling!</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Embodied surprise as the root begins to move</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mother_flure.first.aster.watchout</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Peris, the traje— watch out!</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Starts in data mode; concern cuts him off mid-word</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mother_flure.mechanism.peris.thanks</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Endo! Thank you, thank you!</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bubbly, still in wonder register; touches his arm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mother_flure.mechanism.aster.equipment</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Huh. What equipment did you use to handle that?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>From inside his institutional frame; assumes hazard flag held</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mother_flure.mechanism.endo.flex</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Endo flexes. Small, wordless. He does not explain. The flex is the answer: the equipment was him. A rare, brief Endo smile — he has let himself have this one beat.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The flex is the punchline</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mother_flure.mechanism.endo.door</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Endo turns toward the open door, then back at them. After you.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not going first this time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mother_flure.bloom.peris.scale</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>All of it...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Scale landing before identity; hand may reach out</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mother_flure.bloom.peris.her</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>...it was her...</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pronoun shifts; retroactive recognition of the chamber as her body</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.peris.familiar</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>...this smells familiar!</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bubbly sensory register; catching the dying-flure note</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.peris.tried</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Like the one I tried to tend, but couldn't.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Casually specific; the dead flure named verbally for the first time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.peris.tried.alt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>The smell. I know this smell. Something here is stressed.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fallback if player skipped the dead flure beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.aster.nutech</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Well, it definitely smells less like Nutech in here than it did outside. I sure hope the roots don't have scent receptors...</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dry Aster aside; doesn't engage what Peris recognized</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.peris.tend</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Peris kneels near the mother. She begins to tend — hands finding work with the assurance she has not shown with any flora yet in the game. This is the first flora of this scale she has ever been able to touch. The tending animation runs for its standard duration. The mother has not been tended in a very long time.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Interactive tending beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.bloom_narration</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>The mother blooms. Not at the door opening. Not at the mechanism. At the tending. Her body responds to the first care she has received in decades — petals unfurling, internal structures lighting, smaller offshoots throughout the chamber illuminating in cascading sequence. The chamber's light shifts from diffuse to radiant.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The bloom is the response to care</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mother_flure.afterbloom.peris.bloomed</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Whoa...</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The sound the body makes before words</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mother_flure.aster_beat.watching</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aster is quiet for a moment. He looks at Peris, then at the mother, then at the worn floor patch where the root structures emerge.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The silence is the scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mother_flure.exit.endo.gesture</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Endo gestures toward the chamber's far exit — the one on the opposite side of the mother.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Time to move through, not back</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mother_flure.exit.aster.closer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>We're closer than I thought. If my overlay's reading this right, we're only a few corridors out from the facility approach.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Light, procedural progress check</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mother_flure.exit.peris.look_back</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Peris looks back at the mother one more time. The light is still on her. Then she follows.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Last look before passing through</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mother_flure.exit.narration</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>The chamber dims as they pass through. The mother's light fades back to resting. The smaller offshoots settle into a lower glow. The room holds its new state, waiting. The party emerges on the far side into the next infrastructure segment — whatever the mother's root system grew into on that side.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Closing narration; chamber is transit, not destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_aster.deflect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I'll... make sure those are reported when I get back.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Return-to-simulation framing; institutional deferral</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_aster.beat</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>He stands there. Then he turns and walks back.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Retreat into his work</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.see</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Peris rounds the corner. She sees the bodies. She doesn't speak for a beat. Her hand goes to her stomach.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Discovery; nauseated before words</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.sick</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ugh, I feel sick... these could have been my clients...</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nauseated, not performative</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.approach</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>She steps closer anyway. Kneels by one of them.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Care-mode despite nausea</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.endo_careful</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>You're being careful with them.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>To Endo if nearby; reading his past actions through what she sees</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.endo_nod</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Endo nods.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>If he is there</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.good</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>...Good.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Acknowledging that at least someone has been decent</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mother_flure.discover_peris.return</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>She stands. She returns to the puzzle.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The work continues</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mother_flure.debris_aster.try</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aster pushes against the debris. It doesn't move. He pushes harder. Same result.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mother_flure.debris_aster.line</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>They called me a "critical lever" in my performance report, but I guess being an actual lever wasn't covered...</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dry corporate self-observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mother_flure.debris_peris.try</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Peris pushes against the debris. It doesn't move. She steps back.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mother_flure.debris_peris.line</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Just thinking about lifting this makes my arms hurt...</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sensory register; exhausted physical comedy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.narration</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Peris lingers near the water. Her head turns slightly, testing the air. Aster has stepped away toward a terminal mounted near the wall.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Scene opens; establishes character positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.peris.smell</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>What an odd scent. It's almost clinging onto me somehow.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Concentrating, not alarmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.aster.nutech</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>I don't smell anything but the scent of Nutech Spray. They think they can spray that on everything to make things smell more... modern?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Consumer complaint; focus split between terminal and atmosphere</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.aster.hate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>I hate it, though. It makes my nose sting...</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Personal register rather than analytical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.peris.closer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>I've smelled a ton of Nutech Spray before. It doesn't smell like much of anything to me anymore. Come closer to here, though. It's different.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Inviting him in; her adaptation is implicit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.aster.approach</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aster leaves the terminal and crosses to where Peris is standing near the water.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Physical displacement from terminal to scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dead_flure.entry.aster.ruined</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ugh. That Nutech Spray must've ruined my nose...</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Deflection; blames his instrument rather than accept the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dead_flure.find.narration</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aster is now close enough to see what Peris has been standing near. A low spot in the corridor floor, moisture pooled in the depression, something grown there. Petals gray and flat against the substrate. A dense cluster at the center that has cracked and dried. The root system extends beyond the visible body, still there in the substrate but holding nothing.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>First view of the dead flure</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dead_flure.find.aster.joke</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>If I had to sit here and smell Nutech Spray all day, I'd be like this too...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Still complaining about the spray; accidentally names the institutional cause</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dead_flure.tend.interaction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Peris tends the flure. The interaction runs for its normal duration. Her hands move through the full tending sequence — adjusting substrate, clearing debris, checking the base. The flure does not respond. No glow, no shift in color, no change in the plant's state. The tending completes without effect.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Standard flure-tend animation, failed outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dead_flure.tend.peris.stand</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Peris stands. She brushes the substrate off her hands. She looks at the flure for another beat before turning.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Physical exit from the tending posture</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dead_flure.tend.peris.poor</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Poor little guy.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Small, private, affectionate; goodbye in informal register</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dead_flure.tend.aster.portal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>At least the portal's still usable.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Deflects into pragmatic evaluation; doesn't know how to meet her</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dead_flure.tend.portal_interactive</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The portal terminal adjacent to the dead flure becomes interactable. Entering the portal provides the tutorial for portal use and delivers a consumable item — a one-time HP upgrade that a party member can consume.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Portal + consumable tutorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.aster.curmoric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A jar of Curecumin! I had to grind for two years before they let us have just a shot of Curecumin.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Genuine excitement; reveals simulation past</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.aster.invincible</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Something in that stuff makes you feel invincible.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selling it; pitching the institutional reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.peris.dry</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>So like, every other celebration drink?</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dry; punctures Aster's institutional awe with ordinary knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.aster.swig</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Well, why don't you take a swig and tell me for yourself?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Deflection into invitation; can't argue because she's right</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.consumable</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Peris drinks from the jar. Her HP increases. The consumable is expended.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mechanical delivery of the HP upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.peris.direction</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Wow. That feels like a completely different direction from dizziness and vomiting your guts out...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Second dry puncture; implicitly reveals she has been drunk before</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.aster.soon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yeah. Honestly, once we're back in the sim, I'm going to spend a whole week's rewards on Curecumin. Like, every drink.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Natural continuation; reinforces return-to-sim goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dead_flure.leave.narration</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aster and Peris move on. The party continues forward.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Closing narration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>endo_wall.entry.narration</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The party walks back up the offshoot corridor from the Mother Flure chamber. Endo ahead, Aster and Peris behind. The air is warmer than it was before they entered. The post-bloom chemistry lingers on Peris's clothes and in the corridor itself. Aster has not spoken since they left the chamber.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Scene opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>endo_wall.entry.peris.look</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Peris glances at Aster. She does not say anything. She has been glancing at him every minute or so since they left the chamber. He does not notice.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Physical setup for the arrow-flip beat later</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>endo_wall.barrier.narration</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The corridor opens out from the offshoot. They walk toward shelter 6. After a short distance the wall on the left shows stress: an uneven patch in the biological texture, a section where the barrier has thinned.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Physical marker before Endo stops</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>endo_wall.barrier.aster.overlay</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>data</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Barrier integrity at sixty-one. Dropping about one percent per minute. This is stressed, not failing, but it wants attention.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Overlay read; still data-mode but quietly</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.narration</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Endo stops. He does not turn toward the party or say anything. He walks to the stressed section of the wall, places his hands on it, and begins to work. His hands move in small, practiced motions.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The first silent action</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.aster.confused</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Endo?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Not alarmed; asking what is happening</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.peris.naming</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>He's working.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flat; she saw it immediately</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.aster.overlay</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>...The barrier integrity just ticked up. Sixty-two. Sixty-three. He's stabilizing it. How is he stabilizing it?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Overlay confirming what his eyes almost missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.peris.sit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Peris sits down near the wall, a comfortable distance from Endo. She unhooks her pack and pulls out a small piece of food. She is settling in to wait. She does this without asking.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Physical confirmation that she already knew</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>endo_wall.stop.aster.follow</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aster looks at Peris sitting. He looks at Endo working. He sits down near Peris, more hesitantly.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>He is following her read</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.narration</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Endo works. His hands move on the wall. The texture under his hands begins to even out — the thinned patch slowly thickens, the unevenness smooths. Peris watches him. Aster watches Peris. Time passes.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Composition and waiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.aster.question</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>How did you know he was going to stop?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Quiet, genuine question</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.peris.saw</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>He saw the wall.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.aster.saw_too</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Man, they should really automate these checks sometime...</t>
+          <t>I saw the wall. The overlay flagged it.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aster reacts</t>
+          <t>Not argumentative; trying to understand the gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.peris.different</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>You saw a number. He saw the wall.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Naming what she noticed, not performing cleverness</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>endo_wall.wait.aster.beat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aster looks at the wall. He looks at Endo's hands on it. He looks back at Peris. He does not speak for a moment.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Recognition beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.aster.notice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>You've been watching him.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Quiet observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.peris.mm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mm.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Not confirming, not denying</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.aster.specific</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Since we left the chamber. Every time I looked over. You were watching him.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Specifying so she knows he's observing a pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.peris.beat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Peris looks down at her hands. She does not respond immediately. She is noticing her own attention for the first time.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The arrow flip lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.peris.huh</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>...Huh.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>She did not know</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.aster.careful</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Why?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Not pushing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.peris.dont_know</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>I don't know.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Honest; no answer yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.peris.adding</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I've just been... watching him.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Giving him what she has</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>endo_wall.flip.aster.beat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aster does not push further. He has given her the observation. What she does with it is hers.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The restraint is the care</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.readings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>The mother's iron uptake was at one forty percent of baseline. In the chamber.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Starting somewhere he knows</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.listening</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yeah?</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Inviting him to continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.impossible</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cellular senescence at that stress level caps organisms at a fraction of a normal lifespan. The models predict a few cycles. Maybe a dozen. She has been at one forty for... the terminal said decades.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Getting at something</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.wait</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>So the models are wrong?</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gentle prompting</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.no</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>The models aren't wrong. The models are good. Something else is happening that the models don't account for.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Being precise</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.translate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>She wanted to stay.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plain; her frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.pause</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aster does not answer immediately.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Recognition again</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.doesnt_measure</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>The data doesn't measure wanting.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Careful; not dismissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.know</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I know.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Acknowledging his constraint</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.but</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>But you think she wanted to.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asking her to elaborate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.evidence</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>She stayed. That's what wanting to looks like.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Her epistemology; consistent with his data, adding what his data can't see</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.beat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aster considers this. His overlay is still active. He is looking at Endo working.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Allowing the thought to settle</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>endo_wall.process.aster.models</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>I don't think the models account for that.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Quiet admission; a recognition</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>endo_wall.process.peris.smile</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No. Probably not.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Small, not triumphant</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.narration</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Endo lowers his hands from the wall and steps back. The barrier surface is even, the thinned section filled in, the stress resolved. He stands looking at the wall for a beat longer than the work required. Then he turns toward the party.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Closure gesture</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.aster.overlay</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Integrity at ninety-four percent. Holding.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Data confirmation, quiet</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.aster.stand</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aster stands. Peris stands.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Physical acknowledgment that the work is done</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.aster.thanks</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Thanks, Endo.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Short, sincere</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.endo.nod</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Endo nods. He does not speak.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>His acknowledgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.peris.good</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>You're good at this.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Quiet; direct to Endo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>endo_wall.finish.endo.second_nod</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Endo nods again. Something in his posture is slightly different from the first nod — fractionally more settled, fractionally more present. He does not speak.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Silent character beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.narration</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>The party continues toward shelter 6. Endo walks ahead again. Aster and Peris walk together. The barrier behind them holds. Nobody in the future walking past this section will know who stabilized it.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Closing narration; seeds Endo's upcoming departure</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.peris.quiet</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>He's not going to stay with us.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Small realization, not dramatic; she has been watching him</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.aster.look</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>What?</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>He did not expect this observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.peris.wall</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>He has a wall. That's where he belongs.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Final observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.aster.process</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aster is quiet. He looks ahead at Endo. He does not know what to say.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Accepting the observation without knowing what to do with it</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>endo_wall.continue.narration.close</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>They continue toward shelter 6. The air cools slightly as the Mother Flure's post-bloom chemistry fades from their clothes.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Scene ends; transitions into shelter 6 arrival</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>post_flure.leave.narration</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The corridor beyond the chamber is quieter than the chamber was. The mother's warmth fades with each step. Peris walks with her hand touching the wall. Aster's overlay is still on.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Transition opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>post_flure.smell.narration</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Peris brings her sleeve to her face. She inhales. She lowers her arm. She keeps walking.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Confirming what she already knew; the smell is on her</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>post_flure.smell.aster.overlay</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The atmosphere's clearing up ahead. Filtration's better.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Reading overlay, not reading her</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>post_flure.smell.peris.mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mm.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Not really responding; still in the chamber a little</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>post_flure.change.narration</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The corridor brightens as they walk. The walls are cleaner. The rust patches thin. Aster's overlay shows the particulate count dropping.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Environmental transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>post_flure.change.peris.observation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>It's different here.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Quiet observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>post_flure.change.aster.maintained</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>We're approaching a maintained zone. Infrastructure here has active filtration. Someone tends this.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Reads from overlay; unknowingly uses Peris's verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>post_flure.change.peris.quiet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>...Someone.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Soft; the word carries chamber + Peris + place ahead</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>post_flure.endo.narration</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Endo stops at a branching junction. He looks back past them, past the chamber, toward the way they came. His hand rests against the wall for a moment. Then he moves forward.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>First visible sign of Endo's discomfort moving from his wall</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>post_flure.endo.peris.watch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Peris watches him. She does not speak. Aster does not notice. The party continues.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>She registered something; will not name it</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>post_flure.threshold.narration</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The corridor ends at a wide archway. Beyond it, warm light. Voices. The hum of functioning infrastructure. A Tag Day scan point embedded in the far wall, green indicator cycling on schedule. The party stops at the threshold.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Arrival</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>post_flure.threshold.aster.scan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Scan points are active. Normal operation. We're in a maintained zone now.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Data confirmation; not reading emotional weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>post_flure.threshold.peris.people</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>People still live here.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Quiet, almost to herself; the realization lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>post_flure.threshold.aster.correction</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>...Yeah. They do.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropped out of data mode; stands next to her looking at the same thing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>post_flure.threshold.peris.step</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Peris steps through the archway first. Endo follows. Aster waits a beat before crossing, then follows. The corridor behind them is silent.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Scene ends as they cross</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.open</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The corridor opens into a wider space. A patch of Scarpet is visible ahead, spreading across most of the floor for about fifteen meters. Someone is dragging a large sack across the patch, their back to the party. Moving at a normal walking pace despite the sack's size.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Setup; the incongruity should register before the character is identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.recognize</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Is that... Marco?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Quiet recognition by silhouette</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.turn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Marco pauses his drag, looks back, sees the party. He straightens. He gives a small wave — casual, not effusive. Then he returns to the drag, continuing at his previous pace.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Unfussy acknowledgment; he keeps working</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.scan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>His sack... hang on. Let me read this.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Analyst's curiosity; about to process data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.readout</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The floor under him is Scarpet. That whole patch is Scarpet. And the sack... the weight has to be over three times what he could move on bare floor. It's moving like it's nothing.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Technical, working it out aloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.focus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>He's moving at walking pace.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Observational; registers the naturalness</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.stop</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Marco reaches the edge of the Scarpet. He tries to push the sack one step further onto the bare floor. It barely moves. He puts his hands on his knees, breathing, then straightens. He looks down at the sack with flat resignation.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Physical beat; he's done this before</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>marco.drag.marco.observation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Can't move it past here.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Flat, matter-of-fact, no complaint</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.connect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>It's the Scarpet. The Scarpet was letting him move it. Off the Scarpet, it's too heavy.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The connection landing; rule becomes legible</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>He's carried this sack before. He planned the Scarpet.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Reads the person first, then the technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.prepare</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Marco reaches into his satchel and pulls out a small cloth bag and a vial of clear liquid. He kneels at the edge of the Scarpet and pours a pinch of seeds onto the bare floor. Then he dribbles a small amount of the vial's contents onto the seeds. A faint mist rises.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Practiced sequence; small, efficient, unhurried</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.grow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Small green tendrils push up through the vapor. They spread outward. Within two or three seconds, a new patch of Scarpet has extended the bed by about a meter. The growth rate is visibly impossible.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slightly magical first, slightly technical second</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>marco.drag.marco.casual</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Little trick of the trade. Saves my back.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Utterly unperformed; narrating a small practical move</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.overlay</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>His overlay... the seeds were Scarpet seeds. The liquid was a germination accelerator. The vapor was the reaction heat. That was two-second growth.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Naming the chemistry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.watch</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>...what was the liquid?</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Quiet, focused; the student asking the right question</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>marco.drag.marco.share</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Oh, this? Warm water with a little substrate starter from the Scarpet itself. Scrape the carpet, soak it, let it sit in a corner for a day. The bacteria in the substrate do the work; I just carry the solution around. Everyone should know this. They just don't teach it anymore.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Craftsman sharing a technique; gentle critique of institutional education</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>marco.drag.marco.resume</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Anyway. Safe travels. Don't be a stranger.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Echoes the Pendys log entry register</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>marco.drag.narration.continue</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Marco returns to his sack. He starts pushing it again, now onto the new patch of Scarpet he just grew. The sack slides easily. He continues his drag down the corridor, away from the party, at his previous walking pace.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Unfussy departure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.thought</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>That sack... he was moving a sack that probably weighed as much as both of us combined. Because he laid Scarpet along his route. Because Scarpet reduces friction enough for that to work.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Naming the rule aloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.connect</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>...the gear.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Quiet realization; connects demonstration to the Mother Flure gear</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>marco.drag.aster.catch_up</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>...oh. Oh. Yeah. Yeah, we could have.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The catch-up; curious, slightly amused at the world's layering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>marco.drag.peris.resolve</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>I want to learn that.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Quiet, determined; the skill-unlock trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>marco.drag.skill.unlock.narration</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>The party continues down the corridor. Marco's drag is visible ahead of them for another minute or two before he turns off at an intersection. The Scarpet patches he left along his route fade into the ambient flora of the corridor. Peris's hand is occasionally at her flora-satchel. She is thinking about seeds and water.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Closing beat; forward momentum, not a stop</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>myke.stacks.narration.footsteps</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Light footsteps on the floor plate behind them. Not alarmed footsteps. Not hurried. A person walking the way someone walks when they are approaching a conversation they have been listening to.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Transition into the reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>myke.stacks.narration.turn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aster and Peris turn. A man in a maintenance-class uniform is standing a few meters back, between two server racks. Older than the party by a significant margin. He has been there for some part of the last exchange. He does not apologize for being there. He does not raise his hands. He is just there.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Reveal beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.startle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Oh! Uh. Hi.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Classic Aster startle; defaulting to corporate greeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>myke.stacks.peris.reads</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Peris takes a step that places her slightly behind Aster, reading Myke's face and posture. Her body registers him as not-a-threat within two seconds. She does not speak. She is watching.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Her assessment is faster than Aster's</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.greet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Afternoon.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flat, workplace-standard greeting; the incongruity is the joke</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.observation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Your overlay lights flash at about three rack-rows out. Saw you coming from further than you saw me. Figured I'd wait and see if you were reading what I thought you were reading.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Matter-of-fact; surveillance as competence</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.confused</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Reading...</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Trailing off into the realization</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.confirm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The sensors. The exemptions. The permission IDs that don't exist in the personnel database. All that.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Claiming authorship of the evidence Aster just read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.recog</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>You're... you're the one they were looking for.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slow, dawning; corporate frame takes its first real hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.shrug</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Yup.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>One syllable; not boastful, not apologetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.process</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Why?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Genuine bewilderment; analyst asking a root-cause question</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.answer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Because my readings were right and the system's readings were wrong. And when I flagged it through normal channels, the normalization pipeline cleaned the flags out and my supervisor told me the data was fine. So.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Shortest possible form; 'my supervisor told me the data was fine' is load-bearing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>myke.stacks.peris.quiet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Oh.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>One syllable; recognition of a type she has worked with</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.struggle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>...I had something I was going to say about reporting channels but I can hear it already. Yeah. Okay.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Self-interrupt; corporate frame failing in real time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.pivot</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Look. I've been watching you two for a while now. You're trying to get back. I know the routes. I can escort you as far as the ring junction.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Getting to business</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>myke.stacks.peris.check</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Why?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Waiting for the pitch</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.offer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Because when you get back in, I'd like you to rewrite my file.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The ask; five words carrying the whole thesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.parse</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rewrite your file how?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Analyst asking for specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.plan</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Reclassify my status. "Missing persons, maintenance-class, presumed abducted during unauthorized-activity sweep, recovered by authorized personnel, debriefed, restored to rotation." Standard language. You know the language. You write it every day.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fluent, specific; punches at Aster's class position</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.rescue</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>For the narrative part, you stage the rescue. You come back out here, find me on your own schedule, escort me back through the proper checkpoint. Routine incident report, closed case. I reappear in good standing. No awkward questions about where I've been.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Walking through the scenario; a staged reappearance through legitimate channels</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.pendys</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Your friends on the support team would know the actual reclassification protocol. They run maintenance on it. I saw the log you two were just reading. Whoever @pendys is, they owe you drinks. Call in the favor.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Incorporating the just-read log; credibility hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.pendys</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>They would. They actually would. I mean, we were friends. They helped me out of a bad normalization spike. They said "don't be a stranger."</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Slightly warm; remembering people he likes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>myke.stacks.peris.notice</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Peris notices the warmth in Aster's voice. She does not comment. She files it.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>First flash of who Aster is to people beyond the work context</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>myke.stacks.myke.ethics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Worth naming, though. What I'm asking you to do. The system reclassifies people all the time. Cleans records, moves personnel, reassigns status. Happens every cycle. I'm asking you to do the same thing, for me, so I come out the other side of it. I know what that is. I want you to know what that is. Then you decide.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Moral anchor; naming the ethical structure without self-pity</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>myke.stacks.aster.pause</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aster is quiet for a beat. He is looking at Myke. He is looking at the closet workspace, the notebook, the crossed-out schematics. He is looking at Peris. He does not speak yet.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ethical reasoning in real time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>myke.stacks.peris.nod_or_not</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Peris is watching Aster. She is not directing him. She is there. If he looks at her, her face is neutral. She is not going to decide this for him.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Peris refuses to coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>myke.stacks.choice.accept</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yeah. Okay. We'll do it.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Plain, committed, not performed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>myke.stacks.choice.decline</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I don't... I'm not sure. I can't, right now.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Honest, uncertain, not a refusal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>myke.stacks.accept.myke.nod</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Alright. Thank you.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Small crack; the one moment of vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>myke.stacks.accept.myke.logistics</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>I'll escort you to the ring junction. You know the basics down here now. I know some things you don't. Stick with me, watch where I step. I'll pack up.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Back to practical; maintenance-class instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>myke.stacks.accept.myke.packup</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Myke closes the notebook on the workbench, rolls the tools back into their cloth, slides the cloth into a coverall pocket. The workspace looks, after a few seconds, as though it had never been used. He has done this before.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fast and practiced pack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>myke.stacks.accept.peris.soft</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Myke. We'll do what we said.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Making the commitment legible</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>myke.stacks.accept.myke.ack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I know. Let's move.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Flat acknowledgment; transition cue into escort</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>myke.stacks.decline.myke.ok</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Alright.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Flat, one syllable, not injured</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>myke.stacks.decline.myke.open</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Think about it. I'll be here for a bit. You know where to find me.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Door-left-open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>myke.stacks.decline.myke.return</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Myke turns back toward the workbench. He opens the notebook again. Picks up the small circuit board assembly he was working on when the party first found the workspace. He resumes the delicate work. He is not watching them leave.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Clean and unceremonious return to work</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>myke.stacks.decline.peris.small</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Thank you, Myke.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Quiet, sincere, not apologetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>myke.stacks.decline.myke.back</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Myke</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>...Mhm.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Low acknowledgment without looking up</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>nustle.entry.narration</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The shelter is cold. Aster is sitting against the wall reading his overlay. Endo is asleep. Peris comes in from the planter nook, crosses the room, and sits down next to Aster, close enough that their shoulders touch.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Scene opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nustle.entry.peris.settles</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Peris adjusts, pulls her outer layer back over her lap as a blanket, and leans her weight into his side. She does not ask if this is okay. She just settles.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Physical setup for the scene</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>nustle.word.peris.line</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>I'm just going to nustle in for a minute. It's freezing out there.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Casual; not performing affection</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nustle.aster.catch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nusselt. That's... yeah.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Frame caught the word; not aware he misheard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nustle.aster.transfer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The heat transfer is going to be mostly convective at this contact surface. Conductive through the clothing. We're in the right range for Nusselt to apply.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Data framing as bridge; describing what's physically happening between them</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>nustle.peris.mm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mm.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Letting him talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nustle.aster.dimensionless</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>It's just a dimensionless number. The ratio of convective to conductive heat transfer. Tells you how well warmth moves from one body to another across a boundary.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Explaining his frame the way Peris has explained flora to him</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nustle.peris.no_unit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A number without a unit.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Repeating back; checking she has it</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>nustle.aster.ratio</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Right. You can't measure it directly. You measure two things, the convective transfer and the conductive, and the number only exists in their ratio.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Clarifying; still data mode softened by context</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>nustle.peris.quiet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>But you use it anyway.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Setup for her translation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>nustle.aster.judgment</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>It's the whole basis of judgment calls. Whether your heat exchanger works, whether a barrier is going to hold, whether a system is operating in the regime you want. The ratio tells you what to do.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Epistemic function of dimensionless numbers; not yet aware it comes back to him</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>nustle.peris.thinking</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Peris is quiet for a beat. Not performing thought. Actually thinking.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The pause is the scene's pivot</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nustle.peris.relationship</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>So it's like a relationship.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Simple; lands because it is not performed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>nustle.aster.silence</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aster does not answer immediately. The overlay on his wrist is still faintly on, but his eyes are no longer reading it.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>The pause before the recognition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>nustle.peris.elaborates</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>You can't measure it by itself. You can only see it in how the two things interact. And you use that to decide what to do.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finishing the thought she started</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>nustle.aster.beat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aster does not move. He is looking at the opposite wall. His overlay dims but does not shut off.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Registering what she just did</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>nustle.aster.exactly</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>...Yeah. That's exactly what it is.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Flat, quiet; not data mode, not performing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>nustle.pause</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Beat. Neither speaks. Peris does not follow up. She said the thing and she is letting it sit.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The scene's intimate peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>nustle.close.overlay_off</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aster's overlay dims out completely. He is no longer reading data. He is not doing anything. His body stays still against hers.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Physical signal he has left his frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>nustle.close.peris.warm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>You're warm.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Observation, not compliment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nustle.close.aster.freezing</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>You're freezing.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Observation, not deflection; symmetrical</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>nustle.close.peris.not_anymore</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Not anymore.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Quiet; the exchange is complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>nustle.close.narration</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Peris's head comes to rest against Aster's shoulder. Neither moves again. The shelter's heating hums. Outside, far down the corridor, a Techo clicks, then is silent. The camera holds on the two of them sitting against the wall for several seconds before fading.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Closing narration; scene ends in the middle of a quiet breath</t>
         </is>
       </c>
     </row>
@@ -917,7 +8169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +8845,543 @@
       <c r="F23" t="inlineStr">
         <is>
           <t>Session ends - portal closes and Monos fades out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.narration.enter</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>The session connection indicator pulses softly, waiting. Monos's space on the feed is empty. Peris glances at the clock. Two minutes past start time. Clients run late sometimes. The player is free to move around the workspace while the wait continues.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Transition into free exploration; waiting is diegetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.opening.line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Monos is late! I hate marking no-shows... Maybe I'll take a lap around the room first...</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Light exasperation; choosing movement as somatic regulation; micro-noncompliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_1.line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>This one's doing so well! I wasn't sure she'd take when I moved her from the hallway, but she's really settled in. Look at how she's leaning toward the light...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Species: Pilea peperomioides (Chinese money plant). Warm, relational, gendered pronoun; foreshadows flora mechanic</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_2.line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>This little one, though... I can't tell if she's happy here. The leaves curl at the edges. One of my clients said I should install the stat bar mod, but I think that defeats the point. I want to actually learn about her.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Species: Calathea or Maranta (prayer plant). Diagnostic through observation rather than measurement; choice-structure mirrors her client care</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_3.line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>She smells just like Floral Spring. I saved up for this add-on for ages. I think I smelled the real thing once, at a Tag Day when I was little. Nutech discontinued the physical line before I was old enough to save up. The alternatives mostly made people sneeze. Floral Spring was the nice one. The add-on's so close to what I remember. I've had it running for years.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Species: Jasmine (Jasminum polyanthum). Memory colonized by the commercial product that was marketed as its successor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_4.line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>This one's been with me through a lot. She's such a survivor. Every update. Every outage. She just learned to absorb less. Thrive on what she has. I really admire her.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Species: Haworthia (with Echeveria/Aloe alternates). Admires the exact coping mechanism that is her own psychological injury</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_5.line</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Oh, this one's from a client! They got curious about the game after seeing it in my office. Ended up really getting into it. We did a swap last spring.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Species: Pothos (Epipremnum aureum). Clients engage with her workspace; shared touchpoint; foreshadows Teacher archetype</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_6.line</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>She's my oldest. I've had her since... before I really knew what I was doing with plants. Before I knew I could do anything with plants. She was the first one I met.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Species: Jade plant (Crassula ovata). The surviving witness of her flora-origin moment; backstory held in reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_7.line</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Maybe she's just fussy because she feels far from what she's used to. If it's too wet, she gets upset. If it's too dry, then she'll cry. She needs what she needs.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Species: Boston fern (Nephrolepis exaltata). Empathic reframe + sing-song mnemonic; diagnostic counterpart to plant_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_8.line</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Oh, this one's actually named after one of my clients! Kindest person. Knew how to fix things nobody else could figure out. My whole game broke one morning, all my plants turned into pink blocks, and he came over and sorted it all out. I haven't been out to see him in a while... I should schedule a visit soon.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Species: Spider plant (Chlorophytum comosum). Foreshadows Repairperson in the Act 2 Outer Homes; the intended visit will not happen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.plant_9.line</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I remember when I was a kid, and this plant game was so popular! My clients and I still love it. Makes for a great atmosphere.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Species: Peace lily (Spathiphyllum). Vintage-game reveal; atmosphere as part of her care</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.painting.line</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I wish I knew who the artist was and if art helps get their day going too!</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Empathic reach past her clients to a stranger; 'too' nearly acknowledges her own needs</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.wellness.line</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>They're always pushing these on us. "Take a breath." "You deserve a moment." I guess they mean well. I just... I really like my clients. That's why I do this.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sets up the sanction-arc replacement of her feed with this exact content</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.strike_warning.notification</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ui</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WORKFORCE CONDUCT REVIEW
+SECOND WARNING
+PINNED BY WORKER
+Worker ID: PER-[redacted]
+Classification: Pericytic Care Services, Residential Outreach Division.
+This notice confirms a Second Warning for repeated session-duration non-compliance. Two sessions in the current evaluation window exceeded the department overrun threshold.
+Occurrence 1: prior cycle. Client distress required extended attention. Outcome: First Warning.
+Occurrence 2: later same cycle. Acute client situation required continued presence. Outcome: Second Warning.
+A further comparable overrun may result in corrective action, including suspension of session privileges, caseload reassignment, or referral to Workforce Wellness.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Compliance document; shorter UI register without heavy separator punctuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.strike_warning.line</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>In my defense, the sessions get cut off way too quickly! Only the newer, younger therapists need that much time. I write my notes in a third of the time they give me...</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Deflecting joke that still reveals why the warning exists without spelling out the stakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.notes.line</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Monos was doing better last week. He talked about his mom for the first time. It took months for him to get there. I don't want to lose that.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Professional tenderness; the stake she loses at the Rings</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.logbook.interact</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Peris opens Monos's file in the logbook to begin the no-show procedure. As the file opens, the portal's session connection indicator pulses. Monos is connecting. He appears on the feed, flustered, apologetic, slightly out of breath.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gate interaction — Monos arrives at the moment Peris was about to file the mark</t>
         </is>
       </c>
     </row>
@@ -5829,7 +13618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6284,6 +14073,638 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>Not failure - policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>stacks.rest.narration.open</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The cooling systems hum. The server lights pulse. Aster works through data on his device. Peris sits against the wall, arms around her knees. Nothing outside the alcove is moving.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Opening beat; stillness as the environment's signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stacks.rest.narration.peris_quiet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Peris has not spoken for a while. Her breathing has been uneven. She is looking at her hands.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Physical setup for the break</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.breath</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Peris lets out a long breath that shakes near the end. She brings her hands to her face.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Her body speaks first; voice has not caught up</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.cant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>I can't...</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Shaky; the sentence does not complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.silence</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>She presses her palms against her eyes. Her shoulders are trembling.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The first minute of it; held-in crying</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.try_again</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>I'm sorry. I'm sorry, I don't... I thought I was handling this. I thought I was okay. I'm not. I'm really not.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Apologies first; the wellness framework breaking in real time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.scared</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>I can't stop shaking. I just...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sensory-concrete; body-report before feeling-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.ask</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aster, you seem calm... how are you getting through this?</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Professional vocabulary even while breaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.wait_for_answer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aster does not answer right away. He is considering the question. He is not sure he has been asked it before.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The beat before his response</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.start</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I... hm. I think I'm doing what I know how to do. Which is... data modeling.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>First honest statement about his coping mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.models</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>When you model data, you aren't trying to represent things the way they actually are. The real world is... it's messy. There's too much. Every system has a thousand variables and ten thousand interactions between them, and you can't hold that in your head. You can't even hold it in a computer.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aster in his element; model-talk is where his nervous system regulates</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.focus</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>So you don't try. You decide what matters for the decision you're making, and you model that. Everything else, you let go of. If I'm trying to forecast the load on a conduit, I don't care about the ambient temperature three sectors over. Maybe it affects something downstream. Maybe if I tracked every variable I'd see a pattern. But I'd also never finish the model. So I focus.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Professional content; technically accurate for forecasting models</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.application</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Right now, I'm... I'm focused on getting us to the checkpoint. I'm focused on the route. I'm focused on what my overlay is showing me that I can act on. Everything else, I'm not modeling. Because if I modeled everything, I wouldn't be able to move.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Survival strategy and erasure at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.peris</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I care about getting us there. That's what I'm focused on. That's what my model has. So... that's what I'm using.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The word 'us' carries the weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.listening</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Peris is looking at Aster. Her breathing is steadier than it was. She has taken in what he said. She has also heard the last line. She is holding it.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Shifted to held, not to calm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.huh</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Huh.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Acknowledgment of receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.focus</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Focus on what matters, huh?</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Quiet; testing the phrase in her own register</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.breath_settles</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Peris's shoulders loosen. Her breathing evens. She wipes her face with the back of her hand. She is still scared, but the fear is not crushing her right now. The phrase is doing something for her. She is using it.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anxiety reducing; a small handhold</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>stacks.rest.aster.notice</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>...Better?</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Quiet, tentative; he did not expect his explanation to regulate her</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>stacks.rest.peris.yeah</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yeah. A little.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Honest, small, grateful</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>stacks.rest.narration.close</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Neither says anything else for a while. The cooling systems hum. Aster eventually picks his device back up. Peris eventually unfolds from the wall. The rest beat continues.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Closing narration; scene does not resolve the anxiety</t>
         </is>
       </c>
     </row>
@@ -6298,7 +14719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6770,6 +15191,970 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>Reframe: Endo was the guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring.entry.narration</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The corridor opens into a maintained ring corridor. Lit. Populated. Warm. People walking past on their own routines. The infrastructure is not just intact; it is being actively maintained by systems that still function. After everything, the civilization is still here.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>First view; contrast should be jarring</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring.entry.aster.home</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>There. Look at that. This is still working.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relief, not yet triumph; data he knows how to read</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ring.entry.aster.machine</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Is that a drink machine? That is absolutely a drink machine.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Institutional consumer joy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring.entry.peris.quiet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Peris doesn't respond to the drink machine. She is looking at the people.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Holding something different; reading residents like clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring.entry.endo.wall_touch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Endo touches the corridor wall with the flat of his hand. He holds it there for a moment, as if testing. He moves his hand, touches the next section of wall, holds.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Not his infrastructure; body registers difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring.scatter.peris.notice</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>...Strange.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Quiet; noticed the bubble without naming it</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring.scatter.aster.continue</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The checkpoint should be a couple corridors in. Come on.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Does not pick up what Peris noticed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ring.marco.entry.narration</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>A resident stops mid-step. He sees Peris. His face moves through recognition and then alarm. He checks behind himself, as if verifying that nobody else is watching, and then crosses to them, fast but trying to look like he is not moving fast.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Marco approaches Peris specifically</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ring.marco.entry.marco.warn</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Peris. You shouldn't be here.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Not accusatory; protective</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ring.marco.entry.peris.name</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Monos?</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Caseload name; gentle, surprised</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ring.marco.entry.marco.correct</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Marco. It's Marco now.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Firm but not hostile; deliberately ambiguous between real name and codename</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ring.marco.warn.jeopardize</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>You shouldn't be here. Therapists aren't supposed to see their clients. Everyone knows that. You run into your therapist in person, you keep walking, you don't make eye contact. It can jeopardize their career.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Delivering absorbed institutional logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ring.marco.warn.c_suite</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>And the way you came in here... the three of you walking through like you know where you're going. The c-suite entering places was always a bad sign. When executives started walking the floor, something was about to uproot everyone. People learned to avoid the corridors when leadership was on site.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Residents are reading the party as a leadership inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ring.marco.peris.wellness_start</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Marco, I... I'm just here for a little bit. I've been taking some time to mentally recov—</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Wellness-framing attempt; sentence cuts mid-word</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ring.marco.peris.silence</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Peris stops talking. Her mouth stays slightly open. She looks at Marco. She looks at the corridor. She looks at the scatter pattern of residents visible in the periphery. Something has shifted.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The frame drains without a replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ring.marco.peris.apology</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Marco. I am sorry. I didn't mean to put you in this position. I should go.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Automatic institutional response; sincere but hollow</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ring.marco.exit.marco.brief</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>...Thank you. Take care of yourself, Peris.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>First warmth; saying goodbye</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ring.marco.exit.narration</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Marco turns and crosses the corridor into one of the side passages. He does not look back. He walks at the speed of the scatter. Within a few seconds he is indistinguishable from the other residents moving efficiently away from the party's presence.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Marco rejoins the social pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ring.after_marco.aster.weird</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>That was weird. Is that one of your clients?</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Literal content but not meaning; underinformed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ring.after_marco.peris.quiet</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>...Yeah.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Short; no explanation yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ring.after_marco.aster.move_on</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Well. The checkpoint should be just ahead. Come on.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rounds off the moment procedurally</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ring.after_marco.endo.watch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Endo is looking at Peris. He has not moved. When she looks up and meets his eyes, he nods once — the same nod he gave her at the junction when she said his name. Acknowledgment without agreement. Then he starts walking, staying close to her as the party continues.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Endo's read; callback to the junction nod</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ring.departure.narration</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Endo stops at the junction. He does not announce it. He simply does not take the next step. He looks back the way they came. He looks forward. He looks at Peris, then at Aster.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Silent transition into the departure</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ring.departure.aster.question</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Endo?</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Confused; procedural plan hits unscripted variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ring.departure.peris.read</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Peris looks at Endo. She does not ask what he is doing. She has read his body language across the Rings and now through his stillness at the junction, and she already knows. She nods at him slowly, once.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Returning the nod; acknowledgment, not agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ring.departure.endo.turn</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Endo turns. He starts walking back the way they came. He does not say goodbye. He walks at his normal pace.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Returning home, not abandoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ring.departure.aster.delayed</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Wait — is he...?</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Delayed realization; small edge of hurt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ring.departure.peris.explain</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>He's going home, Aster. We're past where he can go.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Recognition of his nature</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ring.departure.aster.but</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>But the checkpoint is right there. He could wait for us. We're coming back out this way.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Still holding the return-to-sim frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ring.departure.peris.look</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Peris does not respond to Aster's plan. She is watching Endo's back. He has not looked back. He is already a corridor-length away.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Silence carries what she cannot say</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ring.departure.aster.settle</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Aster</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>...Fine. Okay. We can do this without him. Checkpoint's just ahead.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Returns to the frame rather than updating it</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ring.departure.narration.closing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>The party continues forward. Two of them now, where three had been since Section 3B. The corridor narrows slightly. The checkpoint is visible at the end of the next corridor, its indicators green, its arch structure clean and recently maintained. The simulation's infrastructure welcomes them with the calm of a system still running exactly as it was designed to run.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Transitions into the lockout; welcome about to become its opposite</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ouroboros" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nustle" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="love-dimensionless" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="system" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -9024,6 +9025,85 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>system.interact.wrong_character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This needs {name}.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Thought-line when the player walks the wrong character onto a required-character interactable. {name} is replaced with the required character.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -9077,7 +9077,6 @@
           <t>system.interact.wrong_character</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>normal</t>
@@ -9110,7 +9109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10368,6 +10367,134 @@
       <c r="F40" t="inlineStr">
         <is>
           <t>The workplace reads refusal as a medical problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.watering.dry</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Fern's bone dry. Client's late anyway.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Thought pointing the player at the watering beat — the hand-inventory tutorial. The can sits by the desk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.watering.pickup</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Half a can. Enough.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>On picking the watering can up — first item in a hand slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.watering.need_can</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Dry soil. Empty hands.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Player tries to water without holding the can.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>peris.sim_expand.watering.done</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>There. Drink up.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The fern is watered; the can goes down beside it. Unlocks the logbook gate timer-side.</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -612,12 +612,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>click</t>
+          <t>{command}</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Label that appears over the drink machine during tutorial</t>
+          <t>Floating control hint over the drink machine; {command} substitutes the live interact binding (right-click on desktop).</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -10246,7 +10246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>This one's doing so well! I wasn't sure she'd take when I moved her from the hallway, but she's really settled in. Look at how she's leaning toward the light...</t>
+          <t>Growing plants is a dying art nowadays. It used to be such a trend when I was young, and everyone wanted the simple life of maintenance work.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pilea peperomioides (Chinese money plant)</t>
+          <t>Register: reflective, gently nostalgic. Voice direction: Peris is speaking to herself while touching a leaf. 'A dying art' is delivered matter-of-factly. 'Such a trend when I was young' is small private nostalgia. 'Everyone wanted the simple life of maintenance work' is delivered straight; Peris was drawn to it then and still values it now. (Replaces the original Pilea 'doing so well / leaning toward the light' line; reassigned in the May 31 design session, propagated here from the transcript record.)</t>
         </is>
       </c>
     </row>
@@ -11015,12 +11015,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oh, this one's from a client! They got curious about the game after seeing it in my office. Ended up really getting into it. We did a swap last spring.</t>
+          <t>Oh, this one's from a client! They got curious about the game after seeing it in my office. Ended up really getting into it. We did a swap last spring. Sweet person. They were really into curecumin too, kept some of the old natural stuff in a hidden cabinet in their home, the kind that opens and closes three times in a row to reveal the compartment. They told me once, like it was a small secret.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pothos (Epipremnum aureum)</t>
+          <t>Pothos (Epipremnum aureum). Register: warm, conversationally proud, then slightly nostalgic in the curecumin beat. SEED (load-bearing, do not trim): the curecumin-cabinet detail teaches the unguessable open-and-close-three-times mechanism for a permanent stat-boost reward (a Curecumin jar) found in the Teacher's home in the Act 2 Outer Homes scene. The line is the only place that mechanism is taught; a player who skips it cannot solve the cabinet on first contact. Delivered as a fond client memory, not a treasure hint. Client is the Teacher archetype but is not named here, preserving the Act 2 reveal. The curecumin half was previously dropped from this cell and is restored verbatim from simulation_tutorial_expansions.</t>
         </is>
       </c>
     </row>
@@ -11059,12 +11059,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>peris.sim_expand.plant_7.line</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Peris</t>
+          <t>peris.sim_expand.plant_7.look</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11079,19 +11074,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maybe she's just fussy because she feels far from what she's used to. If it's too wet, she gets upset. If it's too dry, then she'll cry. She needs what she needs.</t>
+          <t>Peris notices the watering can on the shelf. She picks it up, holds it a moment, and tips it gently over the soil.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Boston fern (Nephrolepis exaltata)</t>
+          <t>Approach and teaching beat. This is where the tutorial teaches item-use and the hand-inventory slot: Peris picks up the watering can (item enters the hand slot), then uses it on the plant (item-use on a target). The everyday motion of someone who waters regularly; the mechanic is taught through her habit, not through a prompt she narrates.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>peris.sim_expand.plant_8.line</t>
+          <t>peris.sim_expand.plant_7.line</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11111,19 +11106,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oh, this one's actually named after one of my clients! Kindest person. Knew how to fix things nobody else could figure out. My whole game broke one morning, all my plants turned into pink blocks, and he came over and sorted it all out. I haven't been out to see him in a while... I should schedule a visit soon.</t>
+          <t>Did you know that people used to water their plants because it helped them have a sense of time, growth and habit maintenance? Such a beautiful tradition!</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spider plant (Chlorophytum comosum)</t>
+          <t>Register: warm, share-trivia-with-delight, affectionate. Voice direction: Peris is sharing a small fact she finds lovely, the way she might share an anecdote with a client. 'Did you know' opens with her gentle inclusive register. 'Such a beautiful tradition!' closes with real appreciation; the exclamation is felt, not performed. The misunderstanding (that plants do not in fact die without water) lives in what the line does not say: Peris frames watering purely as ritual and habit, never as survival, and never registers that the omission is an omission. Her plants are engineered to stay green, so she has no reference for plants dying from lack of water. The misunderstanding lands on the player, not on her. Carries the engineered-green-plants reveal. (Replaces the retired fern empathy-mirror beat; per the May 31 design session this slot was reassigned from the Boston fern to the watering reflection.)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>peris.sim_expand.plant_9.line</t>
+          <t>peris.sim_expand.plant_7.line_repeat</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11143,19 +11138,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I remember when I was a kid, and this plant game was so popular! My clients and I still love it. Makes for a great atmosphere.</t>
+          <t>I read once that some people even kept a little log of it. What day, how much. Imagine caring for something that carefully, just to mark the time passing.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Peace lily (Spathiphyllum)</t>
+          <t>Fires on re-interaction with plant_7 (after the tradition line). Continues the watering-tradition thread and keeps the misunderstanding load-bearing: Peris still frames watering as pure ritual, never as survival. 'Just to mark the time passing' reinforces that the water does nothing the plant needs, in her understanding; her plants are engineered to stay green. Trigger: repeat interaction only, not first contact.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>peris.sim_expand.painting.line</t>
+          <t>peris.sim_expand.plant_8.line</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11175,19 +11170,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The vibes of this painting really brighten up the room! I wonder if artists ever enjoy their work as much as the people who look at it?</t>
+          <t>Oh, this one's actually named after one of my clients! Kindest person. Knew how to fix things nobody else could figure out. My whole game broke one morning, all my plants turned into pink blocks, and he came over and sorted it all out. I haven't been out to see him in a while... I should schedule a visit soon.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Empathic reach past her clients to a stranger; 'too' nearly acknowledges her own needs</t>
+          <t>Spider plant (Chlorophytum comosum)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>peris.sim_expand.wellness.line</t>
+          <t>peris.sim_expand.plant_9.line</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11207,24 +11202,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>'Take a breath.' 'You deserve a moment.' You know what'd help? If I could replace these with photos of my clients...</t>
+          <t>I remember when this plant game was the thing, when I was a kid! It's old now, I know. My clients and I still love it anyway. They don't make them like they used to.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sets up the sanction-arc replacement of her feed with this exact content</t>
+          <t>Peace lily (Spathiphyllum). Register: enthusiastic, nostalgic, warmly conversational; the most energetically-voiced line in the workspace, a deliberate spike up from her low-key plant register. PAYOFF: establishes Peris's affection for the vintage plant game, which pays off when she reacts with delight to Endo's Clot Lot game at the junction ('Ooh! How vintage!'). 'My clients and I still love it' is the load-bearing phrase: the game is a shared aesthetic touchpoint across years of her clients. Pairs with plant_5, which makes that shared-touchpoint specific via one client who took up the game.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>peris.sim_expand.strike_warning.notification</t>
+          <t>peris.sim_expand.painting.line</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11234,19 +11234,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WORKFORCE CONDUCT STATUS: WARNING (2/3 VIOLATIONS)</t>
+          <t>The vibes of this painting really brighten up the room! I wonder if artists ever enjoy their work as much as the people who look at it?</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Compliance document; shorter UI register without heavy separator punctuation</t>
+          <t>Empathic reach past her clients to a stranger; 'too' nearly acknowledges her own needs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>peris.sim_expand.strike_warning.line</t>
+          <t>peris.sim_expand.wellness.line</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11266,29 +11266,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>In my defense, the sessions get cut off way too quickly! Only the newer, younger therapists need that much time. I write my notes in a third of the time they give me...</t>
+          <t>'Take a breath.' 'You deserve a moment.' You know what'd help? If I could replace these with photos of my clients...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deflecting joke that still reveals why the warning exists without spelling out the stakes</t>
+          <t>Sets up the sanction-arc replacement of her feed with this exact content</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>peris_sim.system.sanction_notice</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SYSTEM</t>
+          <t>peris.sim_expand.strike_warning.notification</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11298,29 +11293,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ROLE PRIVILEGES REVOKED. ENABLING SAFEGUARD MODE</t>
+          <t>WORKFORCE CONDUCT STATUS: WARNING (2/3 VIOLATIONS)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peris receives her final strike after saving Monos.</t>
+          <t>Compliance document; shorter UI register without heavy separator punctuation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>peris_sim.system.wellness_feed</t>
+          <t>peris.sim_expand.strike_warning.line</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SYSTEM</t>
+          <t>Peris</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -11330,29 +11325,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3-Step Mindset Mastery: Techniques for handling stress...</t>
+          <t>In my defense, the sessions get cut off way too quickly! Only the newer, younger therapists need that much time. I write my notes in a third of the time they give me...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>The sanction portal replaces client work with wellness prompts and satisfying content.</t>
+          <t>Deflecting joke that still reveals why the warning exists without spelling out the stakes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>peris_sim.peris.sanction_reaction</t>
+          <t>peris_sim.system.sanction_notice</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PERIS</t>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11362,24 +11357,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The only steps I need are more ones around this room...</t>
+          <t>ROLE PRIVILEGES REVOKED. ENABLING SAFEGUARD MODE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Peris reacts to sanction mode.</t>
+          <t>Peris receives her final strike after saving Monos.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>peris_sim.system.spiral_flash</t>
+          <t>peris_sim.system.wellness_feed</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -11389,24 +11389,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>For one frame, the gel loop tears open into spirals. Then the soap-cutting video resumes, seamless and soft.</t>
+          <t>3-Step Mindset Mastery: Techniques for handling stress...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The spiralverse leaks through the wellness footage for a single frame, the gel loop tearing into spirals before the soothing video reseals. The spiral is the capture motif (the Psyknapse trap, the spiralverse); here it surfaces inside the comfort content, a glimpse of what the wellness layer sits on top of.</t>
+          <t>The sanction portal replaces client work with wellness prompts and satisfying content.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>peris_sim.peris.retro</t>
+          <t>peris_sim.peris.sanction_reaction</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Peris</t>
+          <t>PERIS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11421,29 +11421,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>What even is all this? Looks like some really retro footage...</t>
+          <t>The only steps I need are more ones around this room...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Peris's reaction to the glitch. She does not register the spiral as an intrusion at all; she takes it for part of the footage, just more dated, odd wellness video. The dark irony is that the capture motif surfaces right in front of her and reads to her as nothing, content.</t>
+          <t>Peris reacts to sanction mode.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>peris_sim.worker.okay</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>WORKER</t>
+          <t>peris_sim.system.spiral_flash</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11453,42 +11448,106 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hey, we detected abnormal vital signals. Let's get you looked at.</t>
+          <t>For one frame, the gel loop tears open into spirals. Then the soap-cutting video resumes, seamless and soft.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Adjacent worker reacts as Peris removes the sim equipment.</t>
+          <t>The spiralverse leaks through the wellness footage for a single frame, the gel loop tearing into spirals before the soothing video reseals. The spiral is the capture motif (the Psyknapse trap, the spiralverse); here it surfaces inside the comfort content, a glimpse of what the wellness layer sits on top of.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>peris_sim.peris.retro</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Peris</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>What even is all this? Looks like some really retro footage...</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Peris's reaction to the glitch. She does not register the spiral as an intrusion at all; she takes it for part of the footage, just more dated, odd wellness video. The dark irony is that the capture motif surfaces right in front of her and reads to her as nothing, content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>peris_sim.worker.okay</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>WORKER</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Hey, we detected abnormal vital signals. Let's get you looked at.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Adjacent worker reacts as Peris removes the sim equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>peris_sim.worker.medical</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>WORKER</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Yikes, got sanctioned? How boring. The med bay's a snoozefest. I don't remember a thing!</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>The workplace reads refusal as a medical problem.</t>
         </is>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,31 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Ron pivots to Tag Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aster_sim.drink_again.thought</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>thought</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>I'm all good on drinks for now! Don't wanna be holding my bladder during Tag Day...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Second+ interaction with the drink machine. Light Tag Day foreshadowing.</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -15007,7 +15007,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>junction.peris.ferrolure</t>
+          <t>junction.peris.flure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>There's something on the wall. Iron lure -- ferrolure. If I activate it, they might go for that instead.</t>
+          <t>There's something on the wall. Iron lure -- flure. If I activate it, they might go for that instead.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -15039,7 +15039,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>junction.ferrolure.active</t>
+          <t>junction.flure.active</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FERROLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
+          <t>FLURE ACTIVE  //  SIDEROPHORE LURE  //  18s REMAINING</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -16135,12 +16135,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Something is growing where the water seeps into the wall. A ferrolure. Dormant. Peris is already walking toward it.</t>
+          <t>Something is growing where the water seeps into the wall. A flure. Dormant. Peris is already walking toward it.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quiet coda: Peris finds another ferrolure after the harvest.</t>
+          <t>Quiet coda: Peris finds another flure after the harvest.</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Peris confirms the ferrolure still answers her touch.</t>
+          <t>Peris confirms the flure still answers her touch.</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Introduces the first timed ferrolure crossing as a readable rhythm puzzle.</t>
+          <t>Introduces the first timed flure crossing as a readable rhythm puzzle.</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Escalates the second timed ferrolure window so the player reads rising pressure.</t>
+          <t>Escalates the second timed flure window so the player reads rising pressure.</t>
         </is>
       </c>
     </row>

--- a/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
+++ b/to-rust-as-we-fall/data/dialogue/en/act1.xlsx
@@ -12491,12 +12491,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>The corridor opens onto a walkway, an open span over a deeper dark. Half the railing is gone. Down in the gloom below, shapes that were people.</t>
+          <t>The corridor opens onto an intact walkway, an open span over a deeper dark. At the far end, a Chembrane seal blocks the way. Down in the gloom below, shapes that were people.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bridge description. The fork branches off below this walkway; the party passes directly above it here and sees the enemies and the bodies in the gloom below. The far end of the span gives way and drops them to that sub-level fork. (see GDD 9.5)</t>
+          <t>Bridge description. The fork branches off below this walkway; the party passes directly above it here and sees the enemies and the bodies in the gloom below. The intact span reaches a blocked Chembrane seal; the deck gives way around two-thirds across and drops them to that sub-level fork. (see GDD 9.5)</t>
         </is>
       </c>
     </row>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>...Oh my god, Aster, are these people? That lump's got a broken device, and there's bits of Wonderweave strewn about...</t>
+          <t>...Oh my god, Aster, are these people? That lump's got a broken device, and there's bits of Chembrane strewn about...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
